--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13765" uniqueCount="6887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13767" uniqueCount="6888">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000051-FJI</t>
   </si>
   <si>
     <t>FL-2020-000050-AFG</t>
@@ -21006,7 +21009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6880"/>
+  <dimension ref="A1:G6881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -76064,6 +76067,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6881" spans="1:4">
+      <c r="A6881" t="s">
+        <v>6887</v>
+      </c>
+      <c r="D6881" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13767" uniqueCount="6888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14139" uniqueCount="7074">
   <si>
     <t>code</t>
   </si>
@@ -124,7 +124,565 @@
     <t>EP-2020-000013-MYS</t>
   </si>
   <si>
+    <t>EP-2020-000012-AFG</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-AGO</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-AIA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ALB</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ARE</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ARG</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ARM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ATG</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-AUS</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-AUT</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-AZE</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BDI</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BEL</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BEN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BFA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BGD</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BGR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BHR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BHS</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BIH</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BLR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BLZ</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BMU</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BOL</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BRA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BRB</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BRN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BTN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-BWA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CAN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CHE</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CHL</t>
+  </si>
+  <si>
     <t>EP-2020-000012-CHN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CIV</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CMR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-COD</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-COG</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-COL</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CPV</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CRI</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CUB</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CYM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CYP</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-CZE</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-DEU</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-DJI</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-DMA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-DNK</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-DOM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-DZA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ECU</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-EGY</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ERI</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ESP</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-EST</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ETH</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-FIN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-FJI</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-FRA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GAB</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GBR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GEO</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GHA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GIN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GLP</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GMB</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GNB</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GNQ</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GRC</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GRD</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GTM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GUF</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-GUY</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-HKG</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-HND</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-HRV</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-HTI</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-HUN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-IDN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-IND</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-IRL</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-IRN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-IRQ</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ISL</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ISR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ITA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-JAM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-JOR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-JPN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-KAZ</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-KEN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-KGZ</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-KHM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-KNA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-KOR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-KWT</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-LAO</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-LBN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-LBR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-LBY</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-LCA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-LKA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-LTU</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-LUX</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-LVA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MAC</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MAR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MDA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MDG</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MDV</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MEX</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MKD</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MLI</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MLT</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MMR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MNE</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MNG</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MOZ</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MRT</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MSR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MTQ</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MUS</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-MWI</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-NAM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-NCL</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-NER</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-NGA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-NIC</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-NLD</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-NOR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-NPL</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-NZL</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-OMN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-PAK</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-PAN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-PER</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-PHL</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-PNG</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-POL</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-PRT</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-PRY</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-PSE</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-PYF</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-QAT</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-REU</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ROM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-RUS</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-RWA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SAU</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SDN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SEN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SGP</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SLE</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SLV</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SOM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SRB</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SSD</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-STP</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SUR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SVK</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SVN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SWE</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SWZ</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SYC</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-SYR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-TCA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-TCD</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-TGO</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-THA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-TTO</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-TUN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-TUR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-TWN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-TZA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-UGA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-UKR</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-URY</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-USA</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-UZB</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-VCT</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-VEN</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-VGB</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-VNM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-YEM</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ZAF</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ZMB</t>
+  </si>
+  <si>
+    <t>EP-2020-000012-ZWE</t>
   </si>
   <si>
     <t>FL-2020-000011-MOZ</t>
@@ -21009,7 +21567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6881"/>
+  <dimension ref="A1:G7067"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -76075,6 +76633,1494 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6882" spans="1:4">
+      <c r="A6882" t="s">
+        <v>6888</v>
+      </c>
+      <c r="D6882" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6883" spans="1:4">
+      <c r="A6883" t="s">
+        <v>6889</v>
+      </c>
+      <c r="D6883" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6884" spans="1:4">
+      <c r="A6884" t="s">
+        <v>6890</v>
+      </c>
+      <c r="D6884" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6885" spans="1:4">
+      <c r="A6885" t="s">
+        <v>6891</v>
+      </c>
+      <c r="D6885" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6886" spans="1:4">
+      <c r="A6886" t="s">
+        <v>6892</v>
+      </c>
+      <c r="D6886" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6887" spans="1:4">
+      <c r="A6887" t="s">
+        <v>6893</v>
+      </c>
+      <c r="D6887" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6888" spans="1:4">
+      <c r="A6888" t="s">
+        <v>6894</v>
+      </c>
+      <c r="D6888" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6889" spans="1:4">
+      <c r="A6889" t="s">
+        <v>6895</v>
+      </c>
+      <c r="D6889" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6890" spans="1:4">
+      <c r="A6890" t="s">
+        <v>6896</v>
+      </c>
+      <c r="D6890" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6891" spans="1:4">
+      <c r="A6891" t="s">
+        <v>6897</v>
+      </c>
+      <c r="D6891" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6892" spans="1:4">
+      <c r="A6892" t="s">
+        <v>6898</v>
+      </c>
+      <c r="D6892" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6893" spans="1:4">
+      <c r="A6893" t="s">
+        <v>6899</v>
+      </c>
+      <c r="D6893" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6894" spans="1:4">
+      <c r="A6894" t="s">
+        <v>6900</v>
+      </c>
+      <c r="D6894" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6895" spans="1:4">
+      <c r="A6895" t="s">
+        <v>6901</v>
+      </c>
+      <c r="D6895" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6896" spans="1:4">
+      <c r="A6896" t="s">
+        <v>6902</v>
+      </c>
+      <c r="D6896" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6897" spans="1:4">
+      <c r="A6897" t="s">
+        <v>6903</v>
+      </c>
+      <c r="D6897" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6898" spans="1:4">
+      <c r="A6898" t="s">
+        <v>6904</v>
+      </c>
+      <c r="D6898" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6899" spans="1:4">
+      <c r="A6899" t="s">
+        <v>6905</v>
+      </c>
+      <c r="D6899" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6900" spans="1:4">
+      <c r="A6900" t="s">
+        <v>6906</v>
+      </c>
+      <c r="D6900" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6901" spans="1:4">
+      <c r="A6901" t="s">
+        <v>6907</v>
+      </c>
+      <c r="D6901" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6902" spans="1:4">
+      <c r="A6902" t="s">
+        <v>6908</v>
+      </c>
+      <c r="D6902" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6903" spans="1:4">
+      <c r="A6903" t="s">
+        <v>6909</v>
+      </c>
+      <c r="D6903" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6904" spans="1:4">
+      <c r="A6904" t="s">
+        <v>6910</v>
+      </c>
+      <c r="D6904" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6905" spans="1:4">
+      <c r="A6905" t="s">
+        <v>6911</v>
+      </c>
+      <c r="D6905" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6906" spans="1:4">
+      <c r="A6906" t="s">
+        <v>6912</v>
+      </c>
+      <c r="D6906" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6907" spans="1:4">
+      <c r="A6907" t="s">
+        <v>6913</v>
+      </c>
+      <c r="D6907" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6908" spans="1:4">
+      <c r="A6908" t="s">
+        <v>6914</v>
+      </c>
+      <c r="D6908" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6909" spans="1:4">
+      <c r="A6909" t="s">
+        <v>6915</v>
+      </c>
+      <c r="D6909" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6910" spans="1:4">
+      <c r="A6910" t="s">
+        <v>6916</v>
+      </c>
+      <c r="D6910" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6911" spans="1:4">
+      <c r="A6911" t="s">
+        <v>6917</v>
+      </c>
+      <c r="D6911" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6912" spans="1:4">
+      <c r="A6912" t="s">
+        <v>6918</v>
+      </c>
+      <c r="D6912" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6913" spans="1:4">
+      <c r="A6913" t="s">
+        <v>6919</v>
+      </c>
+      <c r="D6913" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6914" spans="1:4">
+      <c r="A6914" t="s">
+        <v>6920</v>
+      </c>
+      <c r="D6914" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6915" spans="1:4">
+      <c r="A6915" t="s">
+        <v>6921</v>
+      </c>
+      <c r="D6915" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6916" spans="1:4">
+      <c r="A6916" t="s">
+        <v>6922</v>
+      </c>
+      <c r="D6916" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6917" spans="1:4">
+      <c r="A6917" t="s">
+        <v>6923</v>
+      </c>
+      <c r="D6917" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6918" spans="1:4">
+      <c r="A6918" t="s">
+        <v>6924</v>
+      </c>
+      <c r="D6918" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6919" spans="1:4">
+      <c r="A6919" t="s">
+        <v>6925</v>
+      </c>
+      <c r="D6919" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6920" spans="1:4">
+      <c r="A6920" t="s">
+        <v>6926</v>
+      </c>
+      <c r="D6920" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6921" spans="1:4">
+      <c r="A6921" t="s">
+        <v>6927</v>
+      </c>
+      <c r="D6921" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6922" spans="1:4">
+      <c r="A6922" t="s">
+        <v>6928</v>
+      </c>
+      <c r="D6922" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6923" spans="1:4">
+      <c r="A6923" t="s">
+        <v>6929</v>
+      </c>
+      <c r="D6923" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6924" spans="1:4">
+      <c r="A6924" t="s">
+        <v>6930</v>
+      </c>
+      <c r="D6924" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6925" spans="1:4">
+      <c r="A6925" t="s">
+        <v>6931</v>
+      </c>
+      <c r="D6925" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6926" spans="1:4">
+      <c r="A6926" t="s">
+        <v>6932</v>
+      </c>
+      <c r="D6926" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6927" spans="1:4">
+      <c r="A6927" t="s">
+        <v>6933</v>
+      </c>
+      <c r="D6927" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6928" spans="1:4">
+      <c r="A6928" t="s">
+        <v>6934</v>
+      </c>
+      <c r="D6928" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6929" spans="1:4">
+      <c r="A6929" t="s">
+        <v>6935</v>
+      </c>
+      <c r="D6929" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6930" spans="1:4">
+      <c r="A6930" t="s">
+        <v>6936</v>
+      </c>
+      <c r="D6930" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6931" spans="1:4">
+      <c r="A6931" t="s">
+        <v>6937</v>
+      </c>
+      <c r="D6931" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6932" spans="1:4">
+      <c r="A6932" t="s">
+        <v>6938</v>
+      </c>
+      <c r="D6932" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6933" spans="1:4">
+      <c r="A6933" t="s">
+        <v>6939</v>
+      </c>
+      <c r="D6933" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6934" spans="1:4">
+      <c r="A6934" t="s">
+        <v>6940</v>
+      </c>
+      <c r="D6934" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6935" spans="1:4">
+      <c r="A6935" t="s">
+        <v>6941</v>
+      </c>
+      <c r="D6935" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6936" spans="1:4">
+      <c r="A6936" t="s">
+        <v>6942</v>
+      </c>
+      <c r="D6936" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6937" spans="1:4">
+      <c r="A6937" t="s">
+        <v>6943</v>
+      </c>
+      <c r="D6937" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6938" spans="1:4">
+      <c r="A6938" t="s">
+        <v>6944</v>
+      </c>
+      <c r="D6938" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6939" spans="1:4">
+      <c r="A6939" t="s">
+        <v>6945</v>
+      </c>
+      <c r="D6939" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6940" spans="1:4">
+      <c r="A6940" t="s">
+        <v>6946</v>
+      </c>
+      <c r="D6940" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6941" spans="1:4">
+      <c r="A6941" t="s">
+        <v>6947</v>
+      </c>
+      <c r="D6941" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6942" spans="1:4">
+      <c r="A6942" t="s">
+        <v>6948</v>
+      </c>
+      <c r="D6942" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6943" spans="1:4">
+      <c r="A6943" t="s">
+        <v>6949</v>
+      </c>
+      <c r="D6943" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6944" spans="1:4">
+      <c r="A6944" t="s">
+        <v>6950</v>
+      </c>
+      <c r="D6944" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6945" spans="1:4">
+      <c r="A6945" t="s">
+        <v>6951</v>
+      </c>
+      <c r="D6945" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6946" spans="1:4">
+      <c r="A6946" t="s">
+        <v>6952</v>
+      </c>
+      <c r="D6946" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6947" spans="1:4">
+      <c r="A6947" t="s">
+        <v>6953</v>
+      </c>
+      <c r="D6947" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6948" spans="1:4">
+      <c r="A6948" t="s">
+        <v>6954</v>
+      </c>
+      <c r="D6948" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6949" spans="1:4">
+      <c r="A6949" t="s">
+        <v>6955</v>
+      </c>
+      <c r="D6949" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6950" spans="1:4">
+      <c r="A6950" t="s">
+        <v>6956</v>
+      </c>
+      <c r="D6950" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6951" spans="1:4">
+      <c r="A6951" t="s">
+        <v>6957</v>
+      </c>
+      <c r="D6951" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6952" spans="1:4">
+      <c r="A6952" t="s">
+        <v>6958</v>
+      </c>
+      <c r="D6952" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6953" spans="1:4">
+      <c r="A6953" t="s">
+        <v>6959</v>
+      </c>
+      <c r="D6953" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6954" spans="1:4">
+      <c r="A6954" t="s">
+        <v>6960</v>
+      </c>
+      <c r="D6954" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6955" spans="1:4">
+      <c r="A6955" t="s">
+        <v>6961</v>
+      </c>
+      <c r="D6955" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6956" spans="1:4">
+      <c r="A6956" t="s">
+        <v>6962</v>
+      </c>
+      <c r="D6956" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6957" spans="1:4">
+      <c r="A6957" t="s">
+        <v>6963</v>
+      </c>
+      <c r="D6957" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6958" spans="1:4">
+      <c r="A6958" t="s">
+        <v>6964</v>
+      </c>
+      <c r="D6958" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6959" spans="1:4">
+      <c r="A6959" t="s">
+        <v>6965</v>
+      </c>
+      <c r="D6959" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6960" spans="1:4">
+      <c r="A6960" t="s">
+        <v>6966</v>
+      </c>
+      <c r="D6960" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6961" spans="1:4">
+      <c r="A6961" t="s">
+        <v>6967</v>
+      </c>
+      <c r="D6961" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6962" spans="1:4">
+      <c r="A6962" t="s">
+        <v>6968</v>
+      </c>
+      <c r="D6962" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6963" spans="1:4">
+      <c r="A6963" t="s">
+        <v>6969</v>
+      </c>
+      <c r="D6963" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6964" spans="1:4">
+      <c r="A6964" t="s">
+        <v>6970</v>
+      </c>
+      <c r="D6964" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6965" spans="1:4">
+      <c r="A6965" t="s">
+        <v>6971</v>
+      </c>
+      <c r="D6965" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6966" spans="1:4">
+      <c r="A6966" t="s">
+        <v>6972</v>
+      </c>
+      <c r="D6966" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6967" spans="1:4">
+      <c r="A6967" t="s">
+        <v>6973</v>
+      </c>
+      <c r="D6967" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6968" spans="1:4">
+      <c r="A6968" t="s">
+        <v>6974</v>
+      </c>
+      <c r="D6968" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6969" spans="1:4">
+      <c r="A6969" t="s">
+        <v>6975</v>
+      </c>
+      <c r="D6969" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6970" spans="1:4">
+      <c r="A6970" t="s">
+        <v>6976</v>
+      </c>
+      <c r="D6970" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6971" spans="1:4">
+      <c r="A6971" t="s">
+        <v>6977</v>
+      </c>
+      <c r="D6971" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6972" spans="1:4">
+      <c r="A6972" t="s">
+        <v>6978</v>
+      </c>
+      <c r="D6972" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6973" spans="1:4">
+      <c r="A6973" t="s">
+        <v>6979</v>
+      </c>
+      <c r="D6973" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6974" spans="1:4">
+      <c r="A6974" t="s">
+        <v>6980</v>
+      </c>
+      <c r="D6974" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6975" spans="1:4">
+      <c r="A6975" t="s">
+        <v>6981</v>
+      </c>
+      <c r="D6975" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6976" spans="1:4">
+      <c r="A6976" t="s">
+        <v>6982</v>
+      </c>
+      <c r="D6976" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6977" spans="1:4">
+      <c r="A6977" t="s">
+        <v>6983</v>
+      </c>
+      <c r="D6977" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6978" spans="1:4">
+      <c r="A6978" t="s">
+        <v>6984</v>
+      </c>
+      <c r="D6978" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6979" spans="1:4">
+      <c r="A6979" t="s">
+        <v>6985</v>
+      </c>
+      <c r="D6979" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6980" spans="1:4">
+      <c r="A6980" t="s">
+        <v>6986</v>
+      </c>
+      <c r="D6980" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6981" spans="1:4">
+      <c r="A6981" t="s">
+        <v>6987</v>
+      </c>
+      <c r="D6981" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6982" spans="1:4">
+      <c r="A6982" t="s">
+        <v>6988</v>
+      </c>
+      <c r="D6982" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6983" spans="1:4">
+      <c r="A6983" t="s">
+        <v>6989</v>
+      </c>
+      <c r="D6983" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6984" spans="1:4">
+      <c r="A6984" t="s">
+        <v>6990</v>
+      </c>
+      <c r="D6984" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6985" spans="1:4">
+      <c r="A6985" t="s">
+        <v>6991</v>
+      </c>
+      <c r="D6985" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6986" spans="1:4">
+      <c r="A6986" t="s">
+        <v>6992</v>
+      </c>
+      <c r="D6986" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6987" spans="1:4">
+      <c r="A6987" t="s">
+        <v>6993</v>
+      </c>
+      <c r="D6987" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6988" spans="1:4">
+      <c r="A6988" t="s">
+        <v>6994</v>
+      </c>
+      <c r="D6988" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6989" spans="1:4">
+      <c r="A6989" t="s">
+        <v>6995</v>
+      </c>
+      <c r="D6989" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6990" spans="1:4">
+      <c r="A6990" t="s">
+        <v>6996</v>
+      </c>
+      <c r="D6990" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6991" spans="1:4">
+      <c r="A6991" t="s">
+        <v>6997</v>
+      </c>
+      <c r="D6991" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6992" spans="1:4">
+      <c r="A6992" t="s">
+        <v>6998</v>
+      </c>
+      <c r="D6992" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6993" spans="1:4">
+      <c r="A6993" t="s">
+        <v>6999</v>
+      </c>
+      <c r="D6993" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6994" spans="1:4">
+      <c r="A6994" t="s">
+        <v>7000</v>
+      </c>
+      <c r="D6994" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6995" spans="1:4">
+      <c r="A6995" t="s">
+        <v>7001</v>
+      </c>
+      <c r="D6995" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6996" spans="1:4">
+      <c r="A6996" t="s">
+        <v>7002</v>
+      </c>
+      <c r="D6996" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6997" spans="1:4">
+      <c r="A6997" t="s">
+        <v>7003</v>
+      </c>
+      <c r="D6997" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6998" spans="1:4">
+      <c r="A6998" t="s">
+        <v>7004</v>
+      </c>
+      <c r="D6998" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6999" spans="1:4">
+      <c r="A6999" t="s">
+        <v>7005</v>
+      </c>
+      <c r="D6999" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7000" spans="1:4">
+      <c r="A7000" t="s">
+        <v>7006</v>
+      </c>
+      <c r="D7000" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7001" spans="1:4">
+      <c r="A7001" t="s">
+        <v>7007</v>
+      </c>
+      <c r="D7001" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7002" spans="1:4">
+      <c r="A7002" t="s">
+        <v>7008</v>
+      </c>
+      <c r="D7002" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7003" spans="1:4">
+      <c r="A7003" t="s">
+        <v>7009</v>
+      </c>
+      <c r="D7003" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7004" spans="1:4">
+      <c r="A7004" t="s">
+        <v>7010</v>
+      </c>
+      <c r="D7004" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7005" spans="1:4">
+      <c r="A7005" t="s">
+        <v>7011</v>
+      </c>
+      <c r="D7005" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7006" spans="1:4">
+      <c r="A7006" t="s">
+        <v>7012</v>
+      </c>
+      <c r="D7006" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7007" spans="1:4">
+      <c r="A7007" t="s">
+        <v>7013</v>
+      </c>
+      <c r="D7007" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7008" spans="1:4">
+      <c r="A7008" t="s">
+        <v>7014</v>
+      </c>
+      <c r="D7008" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7009" spans="1:4">
+      <c r="A7009" t="s">
+        <v>7015</v>
+      </c>
+      <c r="D7009" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7010" spans="1:4">
+      <c r="A7010" t="s">
+        <v>7016</v>
+      </c>
+      <c r="D7010" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7011" spans="1:4">
+      <c r="A7011" t="s">
+        <v>7017</v>
+      </c>
+      <c r="D7011" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7012" spans="1:4">
+      <c r="A7012" t="s">
+        <v>7018</v>
+      </c>
+      <c r="D7012" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7013" spans="1:4">
+      <c r="A7013" t="s">
+        <v>7019</v>
+      </c>
+      <c r="D7013" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7014" spans="1:4">
+      <c r="A7014" t="s">
+        <v>7020</v>
+      </c>
+      <c r="D7014" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7015" spans="1:4">
+      <c r="A7015" t="s">
+        <v>7021</v>
+      </c>
+      <c r="D7015" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7016" spans="1:4">
+      <c r="A7016" t="s">
+        <v>7022</v>
+      </c>
+      <c r="D7016" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7017" spans="1:4">
+      <c r="A7017" t="s">
+        <v>7023</v>
+      </c>
+      <c r="D7017" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7018" spans="1:4">
+      <c r="A7018" t="s">
+        <v>7024</v>
+      </c>
+      <c r="D7018" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7019" spans="1:4">
+      <c r="A7019" t="s">
+        <v>7025</v>
+      </c>
+      <c r="D7019" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7020" spans="1:4">
+      <c r="A7020" t="s">
+        <v>7026</v>
+      </c>
+      <c r="D7020" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7021" spans="1:4">
+      <c r="A7021" t="s">
+        <v>7027</v>
+      </c>
+      <c r="D7021" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7022" spans="1:4">
+      <c r="A7022" t="s">
+        <v>7028</v>
+      </c>
+      <c r="D7022" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7023" spans="1:4">
+      <c r="A7023" t="s">
+        <v>7029</v>
+      </c>
+      <c r="D7023" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7024" spans="1:4">
+      <c r="A7024" t="s">
+        <v>7030</v>
+      </c>
+      <c r="D7024" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7025" spans="1:4">
+      <c r="A7025" t="s">
+        <v>7031</v>
+      </c>
+      <c r="D7025" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7026" spans="1:4">
+      <c r="A7026" t="s">
+        <v>7032</v>
+      </c>
+      <c r="D7026" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7027" spans="1:4">
+      <c r="A7027" t="s">
+        <v>7033</v>
+      </c>
+      <c r="D7027" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7028" spans="1:4">
+      <c r="A7028" t="s">
+        <v>7034</v>
+      </c>
+      <c r="D7028" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7029" spans="1:4">
+      <c r="A7029" t="s">
+        <v>7035</v>
+      </c>
+      <c r="D7029" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7030" spans="1:4">
+      <c r="A7030" t="s">
+        <v>7036</v>
+      </c>
+      <c r="D7030" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7031" spans="1:4">
+      <c r="A7031" t="s">
+        <v>7037</v>
+      </c>
+      <c r="D7031" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7032" spans="1:4">
+      <c r="A7032" t="s">
+        <v>7038</v>
+      </c>
+      <c r="D7032" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7033" spans="1:4">
+      <c r="A7033" t="s">
+        <v>7039</v>
+      </c>
+      <c r="D7033" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7034" spans="1:4">
+      <c r="A7034" t="s">
+        <v>7040</v>
+      </c>
+      <c r="D7034" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7035" spans="1:4">
+      <c r="A7035" t="s">
+        <v>7041</v>
+      </c>
+      <c r="D7035" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7036" spans="1:4">
+      <c r="A7036" t="s">
+        <v>7042</v>
+      </c>
+      <c r="D7036" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7037" spans="1:4">
+      <c r="A7037" t="s">
+        <v>7043</v>
+      </c>
+      <c r="D7037" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7038" spans="1:4">
+      <c r="A7038" t="s">
+        <v>7044</v>
+      </c>
+      <c r="D7038" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7039" spans="1:4">
+      <c r="A7039" t="s">
+        <v>7045</v>
+      </c>
+      <c r="D7039" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7040" spans="1:4">
+      <c r="A7040" t="s">
+        <v>7046</v>
+      </c>
+      <c r="D7040" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7041" spans="1:4">
+      <c r="A7041" t="s">
+        <v>7047</v>
+      </c>
+      <c r="D7041" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7042" spans="1:4">
+      <c r="A7042" t="s">
+        <v>7048</v>
+      </c>
+      <c r="D7042" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7043" spans="1:4">
+      <c r="A7043" t="s">
+        <v>7049</v>
+      </c>
+      <c r="D7043" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7044" spans="1:4">
+      <c r="A7044" t="s">
+        <v>7050</v>
+      </c>
+      <c r="D7044" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7045" spans="1:4">
+      <c r="A7045" t="s">
+        <v>7051</v>
+      </c>
+      <c r="D7045" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7046" spans="1:4">
+      <c r="A7046" t="s">
+        <v>7052</v>
+      </c>
+      <c r="D7046" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7047" spans="1:4">
+      <c r="A7047" t="s">
+        <v>7053</v>
+      </c>
+      <c r="D7047" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7048" spans="1:4">
+      <c r="A7048" t="s">
+        <v>7054</v>
+      </c>
+      <c r="D7048" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7049" spans="1:4">
+      <c r="A7049" t="s">
+        <v>7055</v>
+      </c>
+      <c r="D7049" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7050" spans="1:4">
+      <c r="A7050" t="s">
+        <v>7056</v>
+      </c>
+      <c r="D7050" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7051" spans="1:4">
+      <c r="A7051" t="s">
+        <v>7057</v>
+      </c>
+      <c r="D7051" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7052" spans="1:4">
+      <c r="A7052" t="s">
+        <v>7058</v>
+      </c>
+      <c r="D7052" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7053" spans="1:4">
+      <c r="A7053" t="s">
+        <v>7059</v>
+      </c>
+      <c r="D7053" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7054" spans="1:4">
+      <c r="A7054" t="s">
+        <v>7060</v>
+      </c>
+      <c r="D7054" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7055" spans="1:4">
+      <c r="A7055" t="s">
+        <v>7061</v>
+      </c>
+      <c r="D7055" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7056" spans="1:4">
+      <c r="A7056" t="s">
+        <v>7062</v>
+      </c>
+      <c r="D7056" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7057" spans="1:4">
+      <c r="A7057" t="s">
+        <v>7063</v>
+      </c>
+      <c r="D7057" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7058" spans="1:4">
+      <c r="A7058" t="s">
+        <v>7064</v>
+      </c>
+      <c r="D7058" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7059" spans="1:4">
+      <c r="A7059" t="s">
+        <v>7065</v>
+      </c>
+      <c r="D7059" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7060" spans="1:4">
+      <c r="A7060" t="s">
+        <v>7066</v>
+      </c>
+      <c r="D7060" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7061" spans="1:4">
+      <c r="A7061" t="s">
+        <v>7067</v>
+      </c>
+      <c r="D7061" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7062" spans="1:4">
+      <c r="A7062" t="s">
+        <v>7068</v>
+      </c>
+      <c r="D7062" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7063" spans="1:4">
+      <c r="A7063" t="s">
+        <v>7069</v>
+      </c>
+      <c r="D7063" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7064" spans="1:4">
+      <c r="A7064" t="s">
+        <v>7070</v>
+      </c>
+      <c r="D7064" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7065" spans="1:4">
+      <c r="A7065" t="s">
+        <v>7071</v>
+      </c>
+      <c r="D7065" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7066" spans="1:4">
+      <c r="A7066" t="s">
+        <v>7072</v>
+      </c>
+      <c r="D7066" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7067" spans="1:4">
+      <c r="A7067" t="s">
+        <v>7073</v>
+      </c>
+      <c r="D7067" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14139" uniqueCount="7074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14141" uniqueCount="7075">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000054-BDI</t>
   </si>
   <si>
     <t>TC-2020-000051-FJI</t>
@@ -21567,7 +21570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7067"/>
+  <dimension ref="A1:G7068"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78121,6 +78124,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7068" spans="1:4">
+      <c r="A7068" t="s">
+        <v>7074</v>
+      </c>
+      <c r="D7068" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14141" uniqueCount="7075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14203" uniqueCount="7106">
   <si>
     <t>code</t>
   </si>
@@ -43,9 +43,30 @@
     <t>en</t>
   </si>
   <si>
+    <t>FF-2020-000123-YEM</t>
+  </si>
+  <si>
+    <t>DR-2020-000122-LKA</t>
+  </si>
+  <si>
+    <t>EP-2020-000120-CAF</t>
+  </si>
+  <si>
+    <t>FL-2020-000069-LAO</t>
+  </si>
+  <si>
+    <t>FF-2020-000055-SOM</t>
+  </si>
+  <si>
     <t>FL-2020-000054-BDI</t>
   </si>
   <si>
+    <t>FF-2020-000053-DJI</t>
+  </si>
+  <si>
+    <t>FL-2020-000052-COD</t>
+  </si>
+  <si>
     <t>TC-2020-000051-FJI</t>
   </si>
   <si>
@@ -895,36 +916,63 @@
     <t>FR-2019-000121-MDV</t>
   </si>
   <si>
+    <t>IN-2019-000121-IND</t>
+  </si>
+  <si>
     <t>FL-2019-000120-PHL</t>
   </si>
   <si>
     <t>EQ-2019-000119-IDN</t>
   </si>
   <si>
+    <t>FL-2019-000119-CMR</t>
+  </si>
+  <si>
     <t>FL-2019-000118-SEN</t>
   </si>
   <si>
+    <t>VO-2019-000118-PNG</t>
+  </si>
+  <si>
     <t>EQ-2019-000117-PAK</t>
   </si>
   <si>
+    <t>FL-2019-000117-SDN</t>
+  </si>
+  <si>
+    <t>EP-2019-000116-PAK</t>
+  </si>
+  <si>
     <t>FL-2019-000116-ETH</t>
   </si>
   <si>
     <t>OT-2019-000115-ZAF</t>
   </si>
   <si>
+    <t>EP-2019-000114-KEN</t>
+  </si>
+  <si>
     <t>EQ-2019-000114-ALB</t>
   </si>
   <si>
+    <t>DR-2019-000113-PHL</t>
+  </si>
+  <si>
     <t>EP-2019-000113-SDN</t>
   </si>
   <si>
     <t>EP-2019-000112-NGA</t>
   </si>
   <si>
+    <t>EP-2019-000112-PHL</t>
+  </si>
+  <si>
     <t>FL-2019-000111-KHM</t>
   </si>
   <si>
+    <t>ST-2019-000111-CUB</t>
+  </si>
+  <si>
     <t>EP-2019-000110-PHL</t>
   </si>
   <si>
@@ -1498,6 +1546,9 @@
     <t>HT-2018-000115-JPN</t>
   </si>
   <si>
+    <t>IN-2018-000115-IND</t>
+  </si>
+  <si>
     <t>EQ-2018-000114-IRN</t>
   </si>
   <si>
@@ -1510,7 +1561,49 @@
     <t>OT-2018-000111-ETH</t>
   </si>
   <si>
+    <t>FL-2018-000110-NIC</t>
+  </si>
+  <si>
     <t>TC-2018-000110-CHN</t>
+  </si>
+  <si>
+    <t>FL-2018-000109-TTO</t>
+  </si>
+  <si>
+    <t>FL-2018-000108-GTM</t>
+  </si>
+  <si>
+    <t>FL-2018-000107-NER</t>
+  </si>
+  <si>
+    <t>DR-2018-000106-SLV</t>
+  </si>
+  <si>
+    <t>FL-2018-000105-BGD</t>
+  </si>
+  <si>
+    <t>EP-2018-000104-COD</t>
+  </si>
+  <si>
+    <t>EP-2018-000103-MWI</t>
+  </si>
+  <si>
+    <t>TC-2018-000102-ASM</t>
+  </si>
+  <si>
+    <t>TC-2018-000102-FJI</t>
+  </si>
+  <si>
+    <t>TC-2018-000102-NIU</t>
+  </si>
+  <si>
+    <t>TC-2018-000102-TON</t>
+  </si>
+  <si>
+    <t>TC-2018-000102-WSM</t>
+  </si>
+  <si>
+    <t>EP-2018-000101-NAM</t>
   </si>
   <si>
     <t>FL-2018-000092-MNG</t>
@@ -21570,7 +21663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7068"/>
+  <dimension ref="A1:G7099"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78132,6 +78225,254 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7069" spans="1:4">
+      <c r="A7069" t="s">
+        <v>7075</v>
+      </c>
+      <c r="D7069" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7070" spans="1:4">
+      <c r="A7070" t="s">
+        <v>7076</v>
+      </c>
+      <c r="D7070" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7071" spans="1:4">
+      <c r="A7071" t="s">
+        <v>7077</v>
+      </c>
+      <c r="D7071" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7072" spans="1:4">
+      <c r="A7072" t="s">
+        <v>7078</v>
+      </c>
+      <c r="D7072" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7073" spans="1:4">
+      <c r="A7073" t="s">
+        <v>7079</v>
+      </c>
+      <c r="D7073" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7074" spans="1:4">
+      <c r="A7074" t="s">
+        <v>7080</v>
+      </c>
+      <c r="D7074" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7075" spans="1:4">
+      <c r="A7075" t="s">
+        <v>7081</v>
+      </c>
+      <c r="D7075" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7076" spans="1:4">
+      <c r="A7076" t="s">
+        <v>7082</v>
+      </c>
+      <c r="D7076" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7077" spans="1:4">
+      <c r="A7077" t="s">
+        <v>7083</v>
+      </c>
+      <c r="D7077" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7078" spans="1:4">
+      <c r="A7078" t="s">
+        <v>7084</v>
+      </c>
+      <c r="D7078" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7079" spans="1:4">
+      <c r="A7079" t="s">
+        <v>7085</v>
+      </c>
+      <c r="D7079" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7080" spans="1:4">
+      <c r="A7080" t="s">
+        <v>7086</v>
+      </c>
+      <c r="D7080" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7081" spans="1:4">
+      <c r="A7081" t="s">
+        <v>7087</v>
+      </c>
+      <c r="D7081" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7082" spans="1:4">
+      <c r="A7082" t="s">
+        <v>7088</v>
+      </c>
+      <c r="D7082" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7083" spans="1:4">
+      <c r="A7083" t="s">
+        <v>7089</v>
+      </c>
+      <c r="D7083" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7084" spans="1:4">
+      <c r="A7084" t="s">
+        <v>7090</v>
+      </c>
+      <c r="D7084" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7085" spans="1:4">
+      <c r="A7085" t="s">
+        <v>7091</v>
+      </c>
+      <c r="D7085" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7086" spans="1:4">
+      <c r="A7086" t="s">
+        <v>7092</v>
+      </c>
+      <c r="D7086" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7087" spans="1:4">
+      <c r="A7087" t="s">
+        <v>7093</v>
+      </c>
+      <c r="D7087" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7088" spans="1:4">
+      <c r="A7088" t="s">
+        <v>7094</v>
+      </c>
+      <c r="D7088" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7089" spans="1:4">
+      <c r="A7089" t="s">
+        <v>7095</v>
+      </c>
+      <c r="D7089" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7090" spans="1:4">
+      <c r="A7090" t="s">
+        <v>7096</v>
+      </c>
+      <c r="D7090" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7091" spans="1:4">
+      <c r="A7091" t="s">
+        <v>7097</v>
+      </c>
+      <c r="D7091" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7092" spans="1:4">
+      <c r="A7092" t="s">
+        <v>7098</v>
+      </c>
+      <c r="D7092" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7093" spans="1:4">
+      <c r="A7093" t="s">
+        <v>7099</v>
+      </c>
+      <c r="D7093" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7094" spans="1:4">
+      <c r="A7094" t="s">
+        <v>7100</v>
+      </c>
+      <c r="D7094" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7095" spans="1:4">
+      <c r="A7095" t="s">
+        <v>7101</v>
+      </c>
+      <c r="D7095" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7096" spans="1:4">
+      <c r="A7096" t="s">
+        <v>7102</v>
+      </c>
+      <c r="D7096" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7097" spans="1:4">
+      <c r="A7097" t="s">
+        <v>7103</v>
+      </c>
+      <c r="D7097" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7098" spans="1:4">
+      <c r="A7098" t="s">
+        <v>7104</v>
+      </c>
+      <c r="D7098" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7099" spans="1:4">
+      <c r="A7099" t="s">
+        <v>7105</v>
+      </c>
+      <c r="D7099" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14203" uniqueCount="7106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14207" uniqueCount="7108">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000126-ETH</t>
+  </si>
+  <si>
+    <t>FL-2020-000125-TZA</t>
   </si>
   <si>
     <t>FF-2020-000123-YEM</t>
@@ -21663,7 +21669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7099"/>
+  <dimension ref="A1:G7101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78473,6 +78479,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7100" spans="1:4">
+      <c r="A7100" t="s">
+        <v>7106</v>
+      </c>
+      <c r="D7100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7101" spans="1:4">
+      <c r="A7101" t="s">
+        <v>7107</v>
+      </c>
+      <c r="D7101" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14207" uniqueCount="7108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14211" uniqueCount="7110">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000130-KAZ</t>
+  </si>
+  <si>
+    <t>EP-2020-000127-ZWE</t>
   </si>
   <si>
     <t>FL-2020-000126-ETH</t>
@@ -21669,7 +21675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7101"/>
+  <dimension ref="A1:G7103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78495,6 +78501,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7102" spans="1:4">
+      <c r="A7102" t="s">
+        <v>7108</v>
+      </c>
+      <c r="D7102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7103" spans="1:4">
+      <c r="A7103" t="s">
+        <v>7109</v>
+      </c>
+      <c r="D7103" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14211" uniqueCount="7110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14213" uniqueCount="7111">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EQ-2020-000131-CUB</t>
   </si>
   <si>
     <t>FL-2020-000130-KAZ</t>
@@ -21675,7 +21678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7103"/>
+  <dimension ref="A1:G7104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78517,6 +78520,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7104" spans="1:4">
+      <c r="A7104" t="s">
+        <v>7110</v>
+      </c>
+      <c r="D7104" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14213" uniqueCount="7111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14217" uniqueCount="7113">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000133-BDI</t>
+  </si>
+  <si>
+    <t>FL-2020-000132-UGA</t>
   </si>
   <si>
     <t>EQ-2020-000131-CUB</t>
@@ -21678,7 +21684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7104"/>
+  <dimension ref="A1:G7106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78528,6 +78534,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7105" spans="1:4">
+      <c r="A7105" t="s">
+        <v>7111</v>
+      </c>
+      <c r="D7105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7106" spans="1:4">
+      <c r="A7106" t="s">
+        <v>7112</v>
+      </c>
+      <c r="D7106" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14217" uniqueCount="7113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14219" uniqueCount="7114">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000134-PHL</t>
   </si>
   <si>
     <t>FL-2020-000133-BDI</t>
@@ -21684,7 +21687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7106"/>
+  <dimension ref="A1:G7107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78550,6 +78553,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7107" spans="1:4">
+      <c r="A7107" t="s">
+        <v>7113</v>
+      </c>
+      <c r="D7107" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14219" uniqueCount="7114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14225" uniqueCount="7117">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,15 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000137-BGD</t>
+  </si>
+  <si>
+    <t>TC-2020-000136-MMR</t>
+  </si>
+  <si>
+    <t>TC-2020-000135-IND</t>
   </si>
   <si>
     <t>TC-2020-000134-PHL</t>
@@ -21687,7 +21696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7107"/>
+  <dimension ref="A1:G7110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78561,6 +78570,30 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7108" spans="1:4">
+      <c r="A7108" t="s">
+        <v>7114</v>
+      </c>
+      <c r="D7108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7109" spans="1:4">
+      <c r="A7109" t="s">
+        <v>7115</v>
+      </c>
+      <c r="D7109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7110" spans="1:4">
+      <c r="A7110" t="s">
+        <v>7116</v>
+      </c>
+      <c r="D7110" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14225" uniqueCount="7117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14227" uniqueCount="7118">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FF-2020-000138-TJK</t>
   </si>
   <si>
     <t>TC-2020-000137-BGD</t>
@@ -21696,7 +21699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7110"/>
+  <dimension ref="A1:G7111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78594,6 +78597,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7111" spans="1:4">
+      <c r="A7111" t="s">
+        <v>7117</v>
+      </c>
+      <c r="D7111" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14227" uniqueCount="7118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14229" uniqueCount="7119">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>IN-2020-000139-NGA</t>
   </si>
   <si>
     <t>FF-2020-000138-TJK</t>
@@ -21699,7 +21702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7111"/>
+  <dimension ref="A1:G7112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78605,6 +78608,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7112" spans="1:4">
+      <c r="A7112" t="s">
+        <v>7118</v>
+      </c>
+      <c r="D7112" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14229" uniqueCount="7119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14233" uniqueCount="7121">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000141-THA</t>
+  </si>
+  <si>
+    <t>FF-2020-000140-IDN</t>
   </si>
   <si>
     <t>IN-2020-000139-NGA</t>
@@ -21702,7 +21708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7112"/>
+  <dimension ref="A1:G7114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78616,6 +78622,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7113" spans="1:4">
+      <c r="A7113" t="s">
+        <v>7119</v>
+      </c>
+      <c r="D7113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7114" spans="1:4">
+      <c r="A7114" t="s">
+        <v>7120</v>
+      </c>
+      <c r="D7114" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14233" uniqueCount="7121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14239" uniqueCount="7124">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,15 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000145-IND</t>
+  </si>
+  <si>
+    <t>SS-2020-000143-CUB</t>
+  </si>
+  <si>
+    <t>TC-2020-000142-SLV</t>
   </si>
   <si>
     <t>TC-2020-000141-THA</t>
@@ -21708,7 +21717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7114"/>
+  <dimension ref="A1:G7117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78638,6 +78647,30 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7115" spans="1:4">
+      <c r="A7115" t="s">
+        <v>7121</v>
+      </c>
+      <c r="D7115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7116" spans="1:4">
+      <c r="A7116" t="s">
+        <v>7122</v>
+      </c>
+      <c r="D7116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7117" spans="1:4">
+      <c r="A7117" t="s">
+        <v>7123</v>
+      </c>
+      <c r="D7117" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14239" uniqueCount="7124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14241" uniqueCount="7125">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000146-SLV</t>
   </si>
   <si>
     <t>TC-2020-000145-IND</t>
@@ -21717,7 +21720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7117"/>
+  <dimension ref="A1:G7118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78671,6 +78674,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7118" spans="1:4">
+      <c r="A7118" t="s">
+        <v>7124</v>
+      </c>
+      <c r="D7118" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14241" uniqueCount="7125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14243" uniqueCount="7126">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000147-CHN</t>
   </si>
   <si>
     <t>TC-2020-000146-SLV</t>
@@ -21720,7 +21723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7118"/>
+  <dimension ref="A1:G7119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78682,6 +78685,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7119" spans="1:4">
+      <c r="A7119" t="s">
+        <v>7125</v>
+      </c>
+      <c r="D7119" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14243" uniqueCount="7126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14251" uniqueCount="7130">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,18 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EP-2020-000151-COD</t>
+  </si>
+  <si>
+    <t>OT-2020-000150-LBY</t>
+  </si>
+  <si>
+    <t>FL-2020-000149-BFA</t>
+  </si>
+  <si>
+    <t>EQ-2020-000148-TUR</t>
   </si>
   <si>
     <t>FL-2020-000147-CHN</t>
@@ -21723,7 +21735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7119"/>
+  <dimension ref="A1:G7123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78693,6 +78705,38 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7120" spans="1:4">
+      <c r="A7120" t="s">
+        <v>7126</v>
+      </c>
+      <c r="D7120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7121" spans="1:4">
+      <c r="A7121" t="s">
+        <v>7127</v>
+      </c>
+      <c r="D7121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7122" spans="1:4">
+      <c r="A7122" t="s">
+        <v>7128</v>
+      </c>
+      <c r="D7122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7123" spans="1:4">
+      <c r="A7123" t="s">
+        <v>7129</v>
+      </c>
+      <c r="D7123" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14251" uniqueCount="7130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14257" uniqueCount="7133">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,15 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000154-CIV</t>
+  </si>
+  <si>
+    <t>FF-2020-000153-BIH</t>
+  </si>
+  <si>
+    <t>OT-2020-000152-MWI</t>
   </si>
   <si>
     <t>EP-2020-000151-COD</t>
@@ -21735,7 +21744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7123"/>
+  <dimension ref="A1:G7126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78737,6 +78746,30 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7124" spans="1:4">
+      <c r="A7124" t="s">
+        <v>7130</v>
+      </c>
+      <c r="D7124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7125" spans="1:4">
+      <c r="A7125" t="s">
+        <v>7131</v>
+      </c>
+      <c r="D7125" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7126" spans="1:4">
+      <c r="A7126" t="s">
+        <v>7132</v>
+      </c>
+      <c r="D7126" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14257" uniqueCount="7133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14263" uniqueCount="7136">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,15 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000157-MYS</t>
+  </si>
+  <si>
+    <t>FF-2020-000156-UKR</t>
+  </si>
+  <si>
+    <t>OT-2020-000155-IDN</t>
   </si>
   <si>
     <t>FL-2020-000154-CIV</t>
@@ -21744,7 +21753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7126"/>
+  <dimension ref="A1:G7129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78770,6 +78779,30 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7127" spans="1:4">
+      <c r="A7127" t="s">
+        <v>7133</v>
+      </c>
+      <c r="D7127" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7128" spans="1:4">
+      <c r="A7128" t="s">
+        <v>7134</v>
+      </c>
+      <c r="D7128" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7129" spans="1:4">
+      <c r="A7129" t="s">
+        <v>7135</v>
+      </c>
+      <c r="D7129" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14263" uniqueCount="7136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14267" uniqueCount="7138">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>OT-2020-000159-MMR</t>
+  </si>
+  <si>
+    <t>FF-2020-000158-SRB</t>
   </si>
   <si>
     <t>FL-2020-000157-MYS</t>
@@ -21753,7 +21759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7129"/>
+  <dimension ref="A1:G7131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78803,6 +78809,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7130" spans="1:4">
+      <c r="A7130" t="s">
+        <v>7136</v>
+      </c>
+      <c r="D7130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7131" spans="1:4">
+      <c r="A7131" t="s">
+        <v>7137</v>
+      </c>
+      <c r="D7131" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14267" uniqueCount="7138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14269" uniqueCount="7139">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000160-JPN</t>
   </si>
   <si>
     <t>OT-2020-000159-MMR</t>
@@ -21759,7 +21762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7131"/>
+  <dimension ref="A1:G7132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78825,6 +78828,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7132" spans="1:4">
+      <c r="A7132" t="s">
+        <v>7138</v>
+      </c>
+      <c r="D7132" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14269" uniqueCount="7139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14273" uniqueCount="7141">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>CE-2020-000162-ETH</t>
+  </si>
+  <si>
+    <t>FL-2020-000161-BGD</t>
   </si>
   <si>
     <t>FL-2020-000160-JPN</t>
@@ -21762,7 +21768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7132"/>
+  <dimension ref="A1:G7134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78836,6 +78842,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7133" spans="1:4">
+      <c r="A7133" t="s">
+        <v>7139</v>
+      </c>
+      <c r="D7133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7134" spans="1:4">
+      <c r="A7134" t="s">
+        <v>7140</v>
+      </c>
+      <c r="D7134" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14273" uniqueCount="7141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14275" uniqueCount="7142">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000164-IND</t>
   </si>
   <si>
     <t>CE-2020-000162-ETH</t>
@@ -21768,7 +21771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7134"/>
+  <dimension ref="A1:G7135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78858,6 +78861,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7135" spans="1:4">
+      <c r="A7135" t="s">
+        <v>7141</v>
+      </c>
+      <c r="D7135" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14275" uniqueCount="7142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14281" uniqueCount="7145">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,15 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>DR-2020-000167-MRT</t>
+  </si>
+  <si>
+    <t>FL-2020-000166-BGD</t>
+  </si>
+  <si>
+    <t>FL-2020-000165-NPL</t>
   </si>
   <si>
     <t>FL-2020-000164-IND</t>
@@ -21771,7 +21780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7135"/>
+  <dimension ref="A1:G7138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78869,6 +78878,30 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7136" spans="1:4">
+      <c r="A7136" t="s">
+        <v>7142</v>
+      </c>
+      <c r="D7136" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7137" spans="1:4">
+      <c r="A7137" t="s">
+        <v>7143</v>
+      </c>
+      <c r="D7137" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7138" spans="1:4">
+      <c r="A7138" t="s">
+        <v>7144</v>
+      </c>
+      <c r="D7138" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14281" uniqueCount="7145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14287" uniqueCount="7148">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,15 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FF-2020-000170-IDN</t>
+  </si>
+  <si>
+    <t>OT-2020-000169-PHL</t>
+  </si>
+  <si>
+    <t>FF-2020-000168-MNG</t>
   </si>
   <si>
     <t>DR-2020-000167-MRT</t>
@@ -21780,7 +21789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7138"/>
+  <dimension ref="A1:G7141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78902,6 +78911,30 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7139" spans="1:4">
+      <c r="A7139" t="s">
+        <v>7145</v>
+      </c>
+      <c r="D7139" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7140" spans="1:4">
+      <c r="A7140" t="s">
+        <v>7146</v>
+      </c>
+      <c r="D7140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7141" spans="1:4">
+      <c r="A7141" t="s">
+        <v>7147</v>
+      </c>
+      <c r="D7141" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14287" uniqueCount="7148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14289" uniqueCount="7149">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000171-ARM</t>
   </si>
   <si>
     <t>FF-2020-000170-IDN</t>
@@ -21789,7 +21792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7141"/>
+  <dimension ref="A1:G7142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78935,6 +78938,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7142" spans="1:4">
+      <c r="A7142" t="s">
+        <v>7148</v>
+      </c>
+      <c r="D7142" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14289" uniqueCount="7149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14303" uniqueCount="7156">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,27 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000178-PRK</t>
+  </si>
+  <si>
+    <t>OT-2020-000177-LBN</t>
+  </si>
+  <si>
+    <t>FL-2020-000176-SDN</t>
+  </si>
+  <si>
+    <t>FL-2020-000175-GEO</t>
+  </si>
+  <si>
+    <t>FR-2020-000174-NAM</t>
+  </si>
+  <si>
+    <t>TC-2020-000173-DOM</t>
+  </si>
+  <si>
+    <t>FL-2020-000172-MMR</t>
   </si>
   <si>
     <t>FL-2020-000171-ARM</t>
@@ -21792,7 +21813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7142"/>
+  <dimension ref="A1:G7149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -78946,6 +78967,62 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7143" spans="1:4">
+      <c r="A7143" t="s">
+        <v>7149</v>
+      </c>
+      <c r="D7143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7144" spans="1:4">
+      <c r="A7144" t="s">
+        <v>7150</v>
+      </c>
+      <c r="D7144" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7145" spans="1:4">
+      <c r="A7145" t="s">
+        <v>7151</v>
+      </c>
+      <c r="D7145" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7146" spans="1:4">
+      <c r="A7146" t="s">
+        <v>7152</v>
+      </c>
+      <c r="D7146" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7147" spans="1:4">
+      <c r="A7147" t="s">
+        <v>7153</v>
+      </c>
+      <c r="D7147" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7148" spans="1:4">
+      <c r="A7148" t="s">
+        <v>7154</v>
+      </c>
+      <c r="D7148" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7149" spans="1:4">
+      <c r="A7149" t="s">
+        <v>7155</v>
+      </c>
+      <c r="D7149" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14303" uniqueCount="7156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14311" uniqueCount="7160">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,18 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000182-CHN</t>
+  </si>
+  <si>
+    <t>OT-2020-000181-BLR</t>
+  </si>
+  <si>
+    <t>AC-2020-000180-MUS</t>
+  </si>
+  <si>
+    <t>FF-2020-000179-IDN</t>
   </si>
   <si>
     <t>TC-2020-000178-PRK</t>
@@ -21813,7 +21825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7149"/>
+  <dimension ref="A1:G7153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79023,6 +79035,38 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7150" spans="1:4">
+      <c r="A7150" t="s">
+        <v>7156</v>
+      </c>
+      <c r="D7150" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7151" spans="1:4">
+      <c r="A7151" t="s">
+        <v>7157</v>
+      </c>
+      <c r="D7151" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7152" spans="1:4">
+      <c r="A7152" t="s">
+        <v>7158</v>
+      </c>
+      <c r="D7152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7153" spans="1:4">
+      <c r="A7153" t="s">
+        <v>7159</v>
+      </c>
+      <c r="D7153" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14311" uniqueCount="7160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14331" uniqueCount="7170">
   <si>
     <t>code</t>
   </si>
@@ -43,6 +43,33 @@
     <t>en</t>
   </si>
   <si>
+    <t>FL-2020-000190-NER</t>
+  </si>
+  <si>
+    <t>TC-2020-000189-HTI</t>
+  </si>
+  <si>
+    <t>TC-2020-000189-USA</t>
+  </si>
+  <si>
+    <t>EQ-2020-000188-DZA</t>
+  </si>
+  <si>
+    <t>FL-2020-000187-KOR</t>
+  </si>
+  <si>
+    <t>EQ-2020-000186-PHL</t>
+  </si>
+  <si>
+    <t>FL-2020-000185-PAK</t>
+  </si>
+  <si>
+    <t>WF-2020-000184-USA</t>
+  </si>
+  <si>
+    <t>HT-2020-000183-JPN</t>
+  </si>
+  <si>
     <t>FL-2020-000182-CHN</t>
   </si>
   <si>
@@ -194,6 +221,9 @@
   </si>
   <si>
     <t>FL-2020-000130-KAZ</t>
+  </si>
+  <si>
+    <t>EP-2020-000129-SDN</t>
   </si>
   <si>
     <t>EP-2020-000127-ZWE</t>
@@ -21825,7 +21855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7153"/>
+  <dimension ref="A1:G7163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79067,6 +79097,86 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7154" spans="1:4">
+      <c r="A7154" t="s">
+        <v>7160</v>
+      </c>
+      <c r="D7154" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7155" spans="1:4">
+      <c r="A7155" t="s">
+        <v>7161</v>
+      </c>
+      <c r="D7155" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7156" spans="1:4">
+      <c r="A7156" t="s">
+        <v>7162</v>
+      </c>
+      <c r="D7156" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7157" spans="1:4">
+      <c r="A7157" t="s">
+        <v>7163</v>
+      </c>
+      <c r="D7157" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7158" spans="1:4">
+      <c r="A7158" t="s">
+        <v>7164</v>
+      </c>
+      <c r="D7158" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7159" spans="1:4">
+      <c r="A7159" t="s">
+        <v>7165</v>
+      </c>
+      <c r="D7159" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7160" spans="1:4">
+      <c r="A7160" t="s">
+        <v>7166</v>
+      </c>
+      <c r="D7160" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7161" spans="1:4">
+      <c r="A7161" t="s">
+        <v>7167</v>
+      </c>
+      <c r="D7161" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7162" spans="1:4">
+      <c r="A7162" t="s">
+        <v>7168</v>
+      </c>
+      <c r="D7162" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7163" spans="1:4">
+      <c r="A7163" t="s">
+        <v>7169</v>
+      </c>
+      <c r="D7163" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14331" uniqueCount="7170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14343" uniqueCount="7176">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,24 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000196-NGA</t>
+  </si>
+  <si>
+    <t>FL-2020-000195-CMR</t>
+  </si>
+  <si>
+    <t>TC-2020-000194-BLZ</t>
+  </si>
+  <si>
+    <t>FL-2020-000193-SSD</t>
+  </si>
+  <si>
+    <t>FL-2020-000192-TCD</t>
+  </si>
+  <si>
+    <t>FF-2020-000191-AFG</t>
   </si>
   <si>
     <t>FL-2020-000190-NER</t>
@@ -21855,7 +21873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7163"/>
+  <dimension ref="A1:G7169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79177,6 +79195,54 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7164" spans="1:4">
+      <c r="A7164" t="s">
+        <v>7170</v>
+      </c>
+      <c r="D7164" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7165" spans="1:4">
+      <c r="A7165" t="s">
+        <v>7171</v>
+      </c>
+      <c r="D7165" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7166" spans="1:4">
+      <c r="A7166" t="s">
+        <v>7172</v>
+      </c>
+      <c r="D7166" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7167" spans="1:4">
+      <c r="A7167" t="s">
+        <v>7173</v>
+      </c>
+      <c r="D7167" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7168" spans="1:4">
+      <c r="A7168" t="s">
+        <v>7174</v>
+      </c>
+      <c r="D7168" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7169" spans="1:4">
+      <c r="A7169" t="s">
+        <v>7175</v>
+      </c>
+      <c r="D7169" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14343" uniqueCount="7176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14347" uniqueCount="7178">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000198-SEN</t>
+  </si>
+  <si>
+    <t>TC-2020-000197-JPN</t>
   </si>
   <si>
     <t>FL-2020-000196-NGA</t>
@@ -21873,7 +21879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7169"/>
+  <dimension ref="A1:G7171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79243,6 +79249,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7170" spans="1:4">
+      <c r="A7170" t="s">
+        <v>7176</v>
+      </c>
+      <c r="D7170" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7171" spans="1:4">
+      <c r="A7171" t="s">
+        <v>7177</v>
+      </c>
+      <c r="D7171" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14347" uniqueCount="7178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14351" uniqueCount="7180">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000200-BFA</t>
+  </si>
+  <si>
+    <t>FL-2020-000199-MRT</t>
   </si>
   <si>
     <t>FL-2020-000198-SEN</t>
@@ -21879,7 +21885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7171"/>
+  <dimension ref="A1:G7173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79265,6 +79271,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7172" spans="1:4">
+      <c r="A7172" t="s">
+        <v>7178</v>
+      </c>
+      <c r="D7172" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7173" spans="1:4">
+      <c r="A7173" t="s">
+        <v>7179</v>
+      </c>
+      <c r="D7173" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14351" uniqueCount="7180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14355" uniqueCount="7182">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000202-GIN</t>
+  </si>
+  <si>
+    <t>EP-2020-000201-YEM</t>
   </si>
   <si>
     <t>FL-2020-000200-BFA</t>
@@ -21885,7 +21891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7173"/>
+  <dimension ref="A1:G7175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79287,6 +79293,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7174" spans="1:4">
+      <c r="A7174" t="s">
+        <v>7180</v>
+      </c>
+      <c r="D7174" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7175" spans="1:4">
+      <c r="A7175" t="s">
+        <v>7181</v>
+      </c>
+      <c r="D7175" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14355" uniqueCount="7182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14357" uniqueCount="7183">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000203-ETH</t>
   </si>
   <si>
     <t>FL-2020-000202-GIN</t>
@@ -21891,7 +21894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7175"/>
+  <dimension ref="A1:G7176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79309,6 +79312,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7176" spans="1:4">
+      <c r="A7176" t="s">
+        <v>7182</v>
+      </c>
+      <c r="D7176" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14357" uniqueCount="7183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14359" uniqueCount="7184">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FF-2020-000204-TUN</t>
   </si>
   <si>
     <t>FL-2020-000203-ETH</t>
@@ -21894,7 +21897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7176"/>
+  <dimension ref="A1:G7177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79320,6 +79323,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7177" spans="1:4">
+      <c r="A7177" t="s">
+        <v>7183</v>
+      </c>
+      <c r="D7177" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14359" uniqueCount="7184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14363" uniqueCount="7186">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000206-COD</t>
+  </si>
+  <si>
+    <t>VO-2020-000205-ECU</t>
   </si>
   <si>
     <t>FF-2020-000204-TUN</t>
@@ -21897,7 +21903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7177"/>
+  <dimension ref="A1:G7179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79331,6 +79337,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7178" spans="1:4">
+      <c r="A7178" t="s">
+        <v>7184</v>
+      </c>
+      <c r="D7178" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7179" spans="1:4">
+      <c r="A7179" t="s">
+        <v>7185</v>
+      </c>
+      <c r="D7179" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14363" uniqueCount="7186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14367" uniqueCount="7188">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FR-2020-000208-SYR</t>
+  </si>
+  <si>
+    <t>FL-2020-000207-NGA</t>
   </si>
   <si>
     <t>FL-2020-000206-COD</t>
@@ -21903,7 +21909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7179"/>
+  <dimension ref="A1:G7181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79353,6 +79359,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7180" spans="1:4">
+      <c r="A7180" t="s">
+        <v>7186</v>
+      </c>
+      <c r="D7180" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7181" spans="1:4">
+      <c r="A7181" t="s">
+        <v>7187</v>
+      </c>
+      <c r="D7181" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14367" uniqueCount="7188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14371" uniqueCount="7190">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000210-VNM</t>
+  </si>
+  <si>
+    <t>OT-2020-000209-AZE</t>
   </si>
   <si>
     <t>FR-2020-000208-SYR</t>
@@ -21909,7 +21915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7181"/>
+  <dimension ref="A1:G7183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79375,6 +79381,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7182" spans="1:4">
+      <c r="A7182" t="s">
+        <v>7188</v>
+      </c>
+      <c r="D7182" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7183" spans="1:4">
+      <c r="A7183" t="s">
+        <v>7189</v>
+      </c>
+      <c r="D7183" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14371" uniqueCount="7190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14373" uniqueCount="7191">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000211-VNM</t>
   </si>
   <si>
     <t>FL-2020-000210-VNM</t>
@@ -21915,7 +21918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7183"/>
+  <dimension ref="A1:G7184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79397,6 +79400,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7184" spans="1:4">
+      <c r="A7184" t="s">
+        <v>7190</v>
+      </c>
+      <c r="D7184" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14373" uniqueCount="7191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14375" uniqueCount="7192">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000212-KHM</t>
   </si>
   <si>
     <t>FL-2020-000211-VNM</t>
@@ -21918,7 +21921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7184"/>
+  <dimension ref="A1:G7185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79408,6 +79411,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7185" spans="1:4">
+      <c r="A7185" t="s">
+        <v>7191</v>
+      </c>
+      <c r="D7185" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14375" uniqueCount="7192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14377" uniqueCount="7193">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2020-000213-LAO</t>
   </si>
   <si>
     <t>FL-2020-000212-KHM</t>
@@ -21921,7 +21924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7185"/>
+  <dimension ref="A1:G7186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79419,6 +79422,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7186" spans="1:4">
+      <c r="A7186" t="s">
+        <v>7192</v>
+      </c>
+      <c r="D7186" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14377" uniqueCount="7193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14379" uniqueCount="7194">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000214-PHL</t>
   </si>
   <si>
     <t>FL-2020-000213-LAO</t>
@@ -21924,7 +21927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7186"/>
+  <dimension ref="A1:G7187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79430,6 +79433,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7187" spans="1:4">
+      <c r="A7187" t="s">
+        <v>7193</v>
+      </c>
+      <c r="D7187" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14379" uniqueCount="7194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14381" uniqueCount="7195">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EQ-2020-000215-TUR</t>
   </si>
   <si>
     <t>TC-2020-000214-PHL</t>
@@ -21927,7 +21930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7187"/>
+  <dimension ref="A1:G7188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79441,6 +79444,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7188" spans="1:4">
+      <c r="A7188" t="s">
+        <v>7194</v>
+      </c>
+      <c r="D7188" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14381" uniqueCount="7195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14385" uniqueCount="7197">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EP-2020-000217-VCT</t>
+  </si>
+  <si>
+    <t>EP-2020-000216-LCA</t>
   </si>
   <si>
     <t>EQ-2020-000215-TUR</t>
@@ -21930,7 +21936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7188"/>
+  <dimension ref="A1:G7190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79452,6 +79458,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7189" spans="1:4">
+      <c r="A7189" t="s">
+        <v>7195</v>
+      </c>
+      <c r="D7189" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7190" spans="1:4">
+      <c r="A7190" t="s">
+        <v>7196</v>
+      </c>
+      <c r="D7190" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14385" uniqueCount="7197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14389" uniqueCount="7199">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>LS-2020-000219-SLV</t>
+  </si>
+  <si>
+    <t>TC-2020-000218-NIC</t>
   </si>
   <si>
     <t>EP-2020-000217-VCT</t>
@@ -21936,7 +21942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7190"/>
+  <dimension ref="A1:G7192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79474,6 +79480,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7191" spans="1:4">
+      <c r="A7191" t="s">
+        <v>7197</v>
+      </c>
+      <c r="D7191" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7192" spans="1:4">
+      <c r="A7192" t="s">
+        <v>7198</v>
+      </c>
+      <c r="D7192" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14389" uniqueCount="7199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14393" uniqueCount="7201">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FF-2020-000221-SOM</t>
+  </si>
+  <si>
+    <t>TC-2020-000220-HND</t>
   </si>
   <si>
     <t>LS-2020-000219-SLV</t>
@@ -21942,7 +21948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7192"/>
+  <dimension ref="A1:G7194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79496,6 +79502,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7193" spans="1:4">
+      <c r="A7193" t="s">
+        <v>7199</v>
+      </c>
+      <c r="D7193" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7194" spans="1:4">
+      <c r="A7194" t="s">
+        <v>7200</v>
+      </c>
+      <c r="D7194" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14393" uniqueCount="7201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14395" uniqueCount="7202">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000222-GTM</t>
   </si>
   <si>
     <t>FF-2020-000221-SOM</t>
@@ -21948,7 +21951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7194"/>
+  <dimension ref="A1:G7195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79518,6 +79521,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7195" spans="1:4">
+      <c r="A7195" t="s">
+        <v>7201</v>
+      </c>
+      <c r="D7195" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14395" uniqueCount="7202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14409" uniqueCount="7209">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,27 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>CE-2020-000229-ETH</t>
+  </si>
+  <si>
+    <t>CE-2020-000228-SDN</t>
+  </si>
+  <si>
+    <t>TC-2020-000227-NIC</t>
+  </si>
+  <si>
+    <t>TC-2020-000226-CRI</t>
+  </si>
+  <si>
+    <t>TC-2020-000225-PHL</t>
+  </si>
+  <si>
+    <t>TC-2020-000224-BLZ</t>
+  </si>
+  <si>
+    <t>IN-2020-000223-ZMB</t>
   </si>
   <si>
     <t>TC-2020-000222-GTM</t>
@@ -21951,7 +21972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7195"/>
+  <dimension ref="A1:G7202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79529,6 +79550,62 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7196" spans="1:4">
+      <c r="A7196" t="s">
+        <v>7202</v>
+      </c>
+      <c r="D7196" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7197" spans="1:4">
+      <c r="A7197" t="s">
+        <v>7203</v>
+      </c>
+      <c r="D7197" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7198" spans="1:4">
+      <c r="A7198" t="s">
+        <v>7204</v>
+      </c>
+      <c r="D7198" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7199" spans="1:4">
+      <c r="A7199" t="s">
+        <v>7205</v>
+      </c>
+      <c r="D7199" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7200" spans="1:4">
+      <c r="A7200" t="s">
+        <v>7206</v>
+      </c>
+      <c r="D7200" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7201" spans="1:4">
+      <c r="A7201" t="s">
+        <v>7207</v>
+      </c>
+      <c r="D7201" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7202" spans="1:4">
+      <c r="A7202" t="s">
+        <v>7208</v>
+      </c>
+      <c r="D7202" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14409" uniqueCount="7209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14411" uniqueCount="7210">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EP-2020-000230-NGA</t>
   </si>
   <si>
     <t>CE-2020-000229-ETH</t>
@@ -21972,7 +21975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7202"/>
+  <dimension ref="A1:G7203"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79606,6 +79609,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7203" spans="1:4">
+      <c r="A7203" t="s">
+        <v>7209</v>
+      </c>
+      <c r="D7203" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14411" uniqueCount="7210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14415" uniqueCount="7212">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000232-SOM</t>
+  </si>
+  <si>
+    <t>DR-2020-000231-MDG</t>
   </si>
   <si>
     <t>EP-2020-000230-NGA</t>
@@ -21975,7 +21981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7203"/>
+  <dimension ref="A1:G7205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79617,6 +79623,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7204" spans="1:4">
+      <c r="A7204" t="s">
+        <v>7210</v>
+      </c>
+      <c r="D7204" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7205" spans="1:4">
+      <c r="A7205" t="s">
+        <v>7211</v>
+      </c>
+      <c r="D7205" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14415" uniqueCount="7212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14421" uniqueCount="7215">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,15 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000235-VNM</t>
+  </si>
+  <si>
+    <t>TC-2020-000234-VNM</t>
+  </si>
+  <si>
+    <t>TC-2020-000233-IND</t>
   </si>
   <si>
     <t>TC-2020-000232-SOM</t>
@@ -21981,7 +21990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7205"/>
+  <dimension ref="A1:G7208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79639,6 +79648,30 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7206" spans="1:4">
+      <c r="A7206" t="s">
+        <v>7212</v>
+      </c>
+      <c r="D7206" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7207" spans="1:4">
+      <c r="A7207" t="s">
+        <v>7213</v>
+      </c>
+      <c r="D7207" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7208" spans="1:4">
+      <c r="A7208" t="s">
+        <v>7214</v>
+      </c>
+      <c r="D7208" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14421" uniqueCount="7215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14423" uniqueCount="7216">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>VO-2020-000236-IDN</t>
   </si>
   <si>
     <t>TC-2020-000235-VNM</t>
@@ -21990,7 +21993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7208"/>
+  <dimension ref="A1:G7209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79672,6 +79675,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7209" spans="1:4">
+      <c r="A7209" t="s">
+        <v>7215</v>
+      </c>
+      <c r="D7209" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14423" uniqueCount="7216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14427" uniqueCount="7218">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000238-FJI</t>
+  </si>
+  <si>
+    <t>FL-2020-000237-LKA</t>
   </si>
   <si>
     <t>VO-2020-000236-IDN</t>
@@ -21993,7 +21999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7209"/>
+  <dimension ref="A1:G7211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79683,6 +79689,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7210" spans="1:4">
+      <c r="A7210" t="s">
+        <v>7216</v>
+      </c>
+      <c r="D7210" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7211" spans="1:4">
+      <c r="A7211" t="s">
+        <v>7217</v>
+      </c>
+      <c r="D7211" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14427" uniqueCount="7218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14429" uniqueCount="7219">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2020-000239-MDG</t>
   </si>
   <si>
     <t>TC-2020-000238-FJI</t>
@@ -21999,7 +22002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7211"/>
+  <dimension ref="A1:G7212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79705,6 +79708,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7212" spans="1:4">
+      <c r="A7212" t="s">
+        <v>7218</v>
+      </c>
+      <c r="D7212" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14429" uniqueCount="7219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14433" uniqueCount="7221">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EQ-2020-000241-HRV</t>
+  </si>
+  <si>
+    <t>FF-2020-000240-ZMB</t>
   </si>
   <si>
     <t>TC-2020-000239-MDG</t>
@@ -22002,7 +22008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7212"/>
+  <dimension ref="A1:G7214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79716,6 +79722,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7213" spans="1:4">
+      <c r="A7213" t="s">
+        <v>7219</v>
+      </c>
+      <c r="D7213" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7214" spans="1:4">
+      <c r="A7214" t="s">
+        <v>7220</v>
+      </c>
+      <c r="D7214" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14433" uniqueCount="7221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14437" uniqueCount="7223">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2021-000001-MYS</t>
+  </si>
+  <si>
+    <t>FL-2020-000242-COL</t>
   </si>
   <si>
     <t>EQ-2020-000241-HRV</t>
@@ -22008,7 +22014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7214"/>
+  <dimension ref="A1:G7216"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79738,6 +79744,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7215" spans="1:4">
+      <c r="A7215" t="s">
+        <v>7221</v>
+      </c>
+      <c r="D7215" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7216" spans="1:4">
+      <c r="A7216" t="s">
+        <v>7222</v>
+      </c>
+      <c r="D7216" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14437" uniqueCount="7223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14439" uniqueCount="7224">
   <si>
     <t>code</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>FL-2021-000001-MYS</t>
+  </si>
+  <si>
+    <t>CW-2020-000243-MNG</t>
   </si>
   <si>
     <t>FL-2020-000242-COL</t>
@@ -22014,7 +22017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7216"/>
+  <dimension ref="A1:G7217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79760,6 +79763,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7217" spans="1:4">
+      <c r="A7217" t="s">
+        <v>7223</v>
+      </c>
+      <c r="D7217" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14439" uniqueCount="7224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14441" uniqueCount="7225">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>CW-2021-000002-JPN</t>
   </si>
   <si>
     <t>FL-2021-000001-MYS</t>
@@ -22017,7 +22020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7217"/>
+  <dimension ref="A1:G7218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79771,6 +79774,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7218" spans="1:4">
+      <c r="A7218" t="s">
+        <v>7224</v>
+      </c>
+      <c r="D7218" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14441" uniqueCount="7225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14445" uniqueCount="7227">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2021-000004-IDN</t>
+  </si>
+  <si>
+    <t>EQ-2021-000003-IDN</t>
   </si>
   <si>
     <t>CW-2021-000002-JPN</t>
@@ -22020,7 +22026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7218"/>
+  <dimension ref="A1:G7220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79782,6 +79788,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7219" spans="1:4">
+      <c r="A7219" t="s">
+        <v>7225</v>
+      </c>
+      <c r="D7219" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7220" spans="1:4">
+      <c r="A7220" t="s">
+        <v>7226</v>
+      </c>
+      <c r="D7220" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14445" uniqueCount="7227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14447" uniqueCount="7228">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2021-000005-IDN</t>
   </si>
   <si>
     <t>FL-2021-000004-IDN</t>
@@ -22026,7 +22029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7220"/>
+  <dimension ref="A1:G7221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79804,6 +79807,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7221" spans="1:4">
+      <c r="A7221" t="s">
+        <v>7227</v>
+      </c>
+      <c r="D7221" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14447" uniqueCount="7228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14449" uniqueCount="7229">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2021-000006-MDG</t>
   </si>
   <si>
     <t>FL-2021-000005-IDN</t>
@@ -22029,7 +22032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7221"/>
+  <dimension ref="A1:G7222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79815,6 +79818,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7222" spans="1:4">
+      <c r="A7222" t="s">
+        <v>7228</v>
+      </c>
+      <c r="D7222" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14449" uniqueCount="7229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14453" uniqueCount="7231">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2021-000008-MOZ</t>
+  </si>
+  <si>
+    <t>FL-2021-000007-SYR</t>
   </si>
   <si>
     <t>TC-2021-000006-MDG</t>
@@ -22032,7 +22038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7222"/>
+  <dimension ref="A1:G7224"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79826,6 +79832,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7223" spans="1:4">
+      <c r="A7223" t="s">
+        <v>7229</v>
+      </c>
+      <c r="D7223" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7224" spans="1:4">
+      <c r="A7224" t="s">
+        <v>7230</v>
+      </c>
+      <c r="D7224" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14453" uniqueCount="7231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14455" uniqueCount="7232">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2021-000009-ZWE</t>
   </si>
   <si>
     <t>TC-2021-000008-MOZ</t>
@@ -22038,7 +22041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7224"/>
+  <dimension ref="A1:G7225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79848,6 +79851,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7225" spans="1:4">
+      <c r="A7225" t="s">
+        <v>7231</v>
+      </c>
+      <c r="D7225" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14455" uniqueCount="7232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14459" uniqueCount="7234">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2021-000011-ZAF</t>
+  </si>
+  <si>
+    <t>OT-2021-000010-IRQ</t>
   </si>
   <si>
     <t>TC-2021-000009-ZWE</t>
@@ -22041,7 +22047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7225"/>
+  <dimension ref="A1:G7227"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79859,6 +79865,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7226" spans="1:4">
+      <c r="A7226" t="s">
+        <v>7232</v>
+      </c>
+      <c r="D7226" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7227" spans="1:4">
+      <c r="A7227" t="s">
+        <v>7233</v>
+      </c>
+      <c r="D7227" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14459" uniqueCount="7234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14463" uniqueCount="7236">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>CE-2021-000013-TCD</t>
+  </si>
+  <si>
+    <t>OT-2021-000012-KEN</t>
   </si>
   <si>
     <t>TC-2021-000011-ZAF</t>
@@ -22047,7 +22053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7227"/>
+  <dimension ref="A1:G7229"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79881,6 +79887,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7228" spans="1:4">
+      <c r="A7228" t="s">
+        <v>7234</v>
+      </c>
+      <c r="D7228" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7229" spans="1:4">
+      <c r="A7229" t="s">
+        <v>7235</v>
+      </c>
+      <c r="D7229" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14463" uniqueCount="7236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14465" uniqueCount="7237">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EP-2021-000014-COD</t>
   </si>
   <si>
     <t>CE-2021-000013-TCD</t>
@@ -22053,7 +22056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7229"/>
+  <dimension ref="A1:G7230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79903,6 +79906,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7230" spans="1:4">
+      <c r="A7230" t="s">
+        <v>7236</v>
+      </c>
+      <c r="D7230" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14465" uniqueCount="7237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14469" uniqueCount="7239">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EP-2021-000016-GIN</t>
+  </si>
+  <si>
+    <t>EQ-2021-000015-JPN</t>
   </si>
   <si>
     <t>EP-2021-000014-COD</t>
@@ -22056,7 +22062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7230"/>
+  <dimension ref="A1:G7232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79914,6 +79920,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7231" spans="1:4">
+      <c r="A7231" t="s">
+        <v>7237</v>
+      </c>
+      <c r="D7231" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7232" spans="1:4">
+      <c r="A7232" t="s">
+        <v>7238</v>
+      </c>
+      <c r="D7232" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14469" uniqueCount="7239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14471" uniqueCount="7240">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2021-000017-PHL</t>
   </si>
   <si>
     <t>EP-2021-000016-GIN</t>
@@ -22062,7 +22065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7232"/>
+  <dimension ref="A1:G7233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79936,6 +79939,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7233" spans="1:4">
+      <c r="A7233" t="s">
+        <v>7239</v>
+      </c>
+      <c r="D7233" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14471" uniqueCount="7240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14473" uniqueCount="7241">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EQ-2021-000018-IRN</t>
   </si>
   <si>
     <t>TC-2021-000017-PHL</t>
@@ -22065,7 +22068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7233"/>
+  <dimension ref="A1:G7234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79947,6 +79950,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7234" spans="1:4">
+      <c r="A7234" t="s">
+        <v>7240</v>
+      </c>
+      <c r="D7234" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14473" uniqueCount="7241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14475" uniqueCount="7242">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2021-000019-PER</t>
   </si>
   <si>
     <t>EQ-2021-000018-IRN</t>
@@ -22068,7 +22071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7234"/>
+  <dimension ref="A1:G7235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79958,6 +79961,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7235" spans="1:4">
+      <c r="A7235" t="s">
+        <v>7241</v>
+      </c>
+      <c r="D7235" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14475" uniqueCount="7242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14505" uniqueCount="7257">
   <si>
     <t>code</t>
   </si>
@@ -43,6 +43,12 @@
     <t>en</t>
   </si>
   <si>
+    <t>FL-2021-000021-IND</t>
+  </si>
+  <si>
+    <t>AC-2021-000020-GNQ</t>
+  </si>
+  <si>
     <t>FL-2021-000019-PER</t>
   </si>
   <si>
@@ -1148,6 +1154,45 @@
   </si>
   <si>
     <t>EQ-2020-000001-PRI</t>
+  </si>
+  <si>
+    <t>ST-2019-000199-USA</t>
+  </si>
+  <si>
+    <t>ST-2019-000197-USA</t>
+  </si>
+  <si>
+    <t>ST-2019-000196-USA</t>
+  </si>
+  <si>
+    <t>TO-2019-000195-USA</t>
+  </si>
+  <si>
+    <t>FL-2019-000194-USA</t>
+  </si>
+  <si>
+    <t>FL-2019-000193-USA</t>
+  </si>
+  <si>
+    <t>FL-2019-000192-USA</t>
+  </si>
+  <si>
+    <t>ST-2019-000191-USA</t>
+  </si>
+  <si>
+    <t>TO-2019-000190-USA</t>
+  </si>
+  <si>
+    <t>ST-2019-000189-USA</t>
+  </si>
+  <si>
+    <t>ST-2019-000188-USA</t>
+  </si>
+  <si>
+    <t>WF-2019-000187-USA</t>
+  </si>
+  <si>
+    <t>TC-2019-000186-USA</t>
   </si>
   <si>
     <t>EP-2019-000184-BGD</t>
@@ -22071,7 +22116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7235"/>
+  <dimension ref="A1:G7250"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -79969,6 +80014,126 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7236" spans="1:4">
+      <c r="A7236" t="s">
+        <v>7242</v>
+      </c>
+      <c r="D7236" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7237" spans="1:4">
+      <c r="A7237" t="s">
+        <v>7243</v>
+      </c>
+      <c r="D7237" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7238" spans="1:4">
+      <c r="A7238" t="s">
+        <v>7244</v>
+      </c>
+      <c r="D7238" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7239" spans="1:4">
+      <c r="A7239" t="s">
+        <v>7245</v>
+      </c>
+      <c r="D7239" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7240" spans="1:4">
+      <c r="A7240" t="s">
+        <v>7246</v>
+      </c>
+      <c r="D7240" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7241" spans="1:4">
+      <c r="A7241" t="s">
+        <v>7247</v>
+      </c>
+      <c r="D7241" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7242" spans="1:4">
+      <c r="A7242" t="s">
+        <v>7248</v>
+      </c>
+      <c r="D7242" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7243" spans="1:4">
+      <c r="A7243" t="s">
+        <v>7249</v>
+      </c>
+      <c r="D7243" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7244" spans="1:4">
+      <c r="A7244" t="s">
+        <v>7250</v>
+      </c>
+      <c r="D7244" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7245" spans="1:4">
+      <c r="A7245" t="s">
+        <v>7251</v>
+      </c>
+      <c r="D7245" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7246" spans="1:4">
+      <c r="A7246" t="s">
+        <v>7252</v>
+      </c>
+      <c r="D7246" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7247" spans="1:4">
+      <c r="A7247" t="s">
+        <v>7253</v>
+      </c>
+      <c r="D7247" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7248" spans="1:4">
+      <c r="A7248" t="s">
+        <v>7254</v>
+      </c>
+      <c r="D7248" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7249" spans="1:4">
+      <c r="A7249" t="s">
+        <v>7255</v>
+      </c>
+      <c r="D7249" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7250" spans="1:4">
+      <c r="A7250" t="s">
+        <v>7256</v>
+      </c>
+      <c r="D7250" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14505" uniqueCount="7257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14509" uniqueCount="7259">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2021-000023-DZA</t>
+  </si>
+  <si>
+    <t>DR-2021-000022-AFG</t>
   </si>
   <si>
     <t>FL-2021-000021-IND</t>
@@ -22116,7 +22122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7250"/>
+  <dimension ref="A1:G7252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -80134,6 +80140,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7251" spans="1:4">
+      <c r="A7251" t="s">
+        <v>7257</v>
+      </c>
+      <c r="D7251" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7252" spans="1:4">
+      <c r="A7252" t="s">
+        <v>7258</v>
+      </c>
+      <c r="D7252" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14509" uniqueCount="7259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14511" uniqueCount="7260">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>ST-2021-000024-MNG</t>
   </si>
   <si>
     <t>FL-2021-000023-DZA</t>
@@ -22122,7 +22125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7252"/>
+  <dimension ref="A1:G7253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -80156,6 +80159,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7253" spans="1:4">
+      <c r="A7253" t="s">
+        <v>7259</v>
+      </c>
+      <c r="D7253" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14511" uniqueCount="7260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14515" uniqueCount="7262">
   <si>
     <t>code</t>
   </si>
@@ -43,6 +43,9 @@
     <t>en</t>
   </si>
   <si>
+    <t>FL-2021-000025-AUS</t>
+  </si>
+  <si>
     <t>ST-2021-000024-MNG</t>
   </si>
   <si>
@@ -113,6 +116,9 @@
   </si>
   <si>
     <t>FL-2021-000001-MYS</t>
+  </si>
+  <si>
+    <t>VO-2020-000244-VCT</t>
   </si>
   <si>
     <t>CW-2020-000243-MNG</t>
@@ -22125,7 +22131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7253"/>
+  <dimension ref="A1:G7255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -80167,6 +80173,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7254" spans="1:4">
+      <c r="A7254" t="s">
+        <v>7260</v>
+      </c>
+      <c r="D7254" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7255" spans="1:4">
+      <c r="A7255" t="s">
+        <v>7261</v>
+      </c>
+      <c r="D7255" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14515" uniqueCount="7262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14519" uniqueCount="7264">
   <si>
     <t>code</t>
   </si>
@@ -43,7 +43,13 @@
     <t>en</t>
   </si>
   <si>
+    <t>CE-2021-000026-GMB</t>
+  </si>
+  <si>
     <t>FL-2021-000025-AUS</t>
+  </si>
+  <si>
+    <t>ST-2021-000024-CHN</t>
   </si>
   <si>
     <t>ST-2021-000024-MNG</t>
@@ -22131,7 +22137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7255"/>
+  <dimension ref="A1:G7257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -80189,6 +80195,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7256" spans="1:4">
+      <c r="A7256" t="s">
+        <v>7262</v>
+      </c>
+      <c r="D7256" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7257" spans="1:4">
+      <c r="A7257" t="s">
+        <v>7263</v>
+      </c>
+      <c r="D7257" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14519" uniqueCount="7264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14521" uniqueCount="7265">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FR-2021-000027-BGD</t>
   </si>
   <si>
     <t>CE-2021-000026-GMB</t>
@@ -22137,7 +22140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7257"/>
+  <dimension ref="A1:G7258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -80211,6 +80214,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7258" spans="1:4">
+      <c r="A7258" t="s">
+        <v>7264</v>
+      </c>
+      <c r="D7258" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17047" uniqueCount="8528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17089" uniqueCount="8549">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,69 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>LS-2025-000165-MYS</t>
+  </si>
+  <si>
+    <t>EQ-2025-000164-IND</t>
+  </si>
+  <si>
+    <t>WF-2025-000163-BOL</t>
+  </si>
+  <si>
+    <t>EQ-2025-000162-RUS</t>
+  </si>
+  <si>
+    <t>FL-2025-000161-IDN</t>
+  </si>
+  <si>
+    <t>TC-2025-000160-CHN</t>
+  </si>
+  <si>
+    <t>EQ-2025-000159-AFG</t>
+  </si>
+  <si>
+    <t>FL-2025-000158-SSD</t>
+  </si>
+  <si>
+    <t>EP-2025-000157-COD</t>
+  </si>
+  <si>
+    <t>EQ-2025-000156-AFG</t>
+  </si>
+  <si>
+    <t>FR-2025-000155-KAZ</t>
+  </si>
+  <si>
+    <t>FL-2025-000154-SDN</t>
+  </si>
+  <si>
+    <t>EQ-2025-000153-AFG</t>
+  </si>
+  <si>
+    <t>DR-2025-000152-SYR</t>
+  </si>
+  <si>
+    <t>FL-2025-000151-YEM</t>
+  </si>
+  <si>
+    <t>FL-2025-000150-GIN</t>
+  </si>
+  <si>
+    <t>EP-2025-000149-TCD</t>
+  </si>
+  <si>
+    <t>DR-2025-000148-ETH</t>
+  </si>
+  <si>
+    <t>FL-2025-000147-CPV</t>
+  </si>
+  <si>
+    <t>FL-2025-000146-CPV</t>
+  </si>
+  <si>
+    <t>FL-2025-000145-GNQ</t>
   </si>
   <si>
     <t>TC-2025-000144-VNM</t>
@@ -25929,7 +25992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8521"/>
+  <dimension ref="A1:G8542"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94115,6 +94178,174 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8522" spans="1:4">
+      <c r="A8522" t="s">
+        <v>8528</v>
+      </c>
+      <c r="D8522" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8523" spans="1:4">
+      <c r="A8523" t="s">
+        <v>8529</v>
+      </c>
+      <c r="D8523" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8524" spans="1:4">
+      <c r="A8524" t="s">
+        <v>8530</v>
+      </c>
+      <c r="D8524" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8525" spans="1:4">
+      <c r="A8525" t="s">
+        <v>8531</v>
+      </c>
+      <c r="D8525" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8526" spans="1:4">
+      <c r="A8526" t="s">
+        <v>8532</v>
+      </c>
+      <c r="D8526" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8527" spans="1:4">
+      <c r="A8527" t="s">
+        <v>8533</v>
+      </c>
+      <c r="D8527" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8528" spans="1:4">
+      <c r="A8528" t="s">
+        <v>8534</v>
+      </c>
+      <c r="D8528" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8529" spans="1:4">
+      <c r="A8529" t="s">
+        <v>8535</v>
+      </c>
+      <c r="D8529" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8530" spans="1:4">
+      <c r="A8530" t="s">
+        <v>8536</v>
+      </c>
+      <c r="D8530" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8531" spans="1:4">
+      <c r="A8531" t="s">
+        <v>8537</v>
+      </c>
+      <c r="D8531" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8532" spans="1:4">
+      <c r="A8532" t="s">
+        <v>8538</v>
+      </c>
+      <c r="D8532" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8533" spans="1:4">
+      <c r="A8533" t="s">
+        <v>8539</v>
+      </c>
+      <c r="D8533" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8534" spans="1:4">
+      <c r="A8534" t="s">
+        <v>8540</v>
+      </c>
+      <c r="D8534" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8535" spans="1:4">
+      <c r="A8535" t="s">
+        <v>8541</v>
+      </c>
+      <c r="D8535" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8536" spans="1:4">
+      <c r="A8536" t="s">
+        <v>8542</v>
+      </c>
+      <c r="D8536" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8537" spans="1:4">
+      <c r="A8537" t="s">
+        <v>8543</v>
+      </c>
+      <c r="D8537" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8538" spans="1:4">
+      <c r="A8538" t="s">
+        <v>8544</v>
+      </c>
+      <c r="D8538" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8539" spans="1:4">
+      <c r="A8539" t="s">
+        <v>8545</v>
+      </c>
+      <c r="D8539" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8540" spans="1:4">
+      <c r="A8540" t="s">
+        <v>8546</v>
+      </c>
+      <c r="D8540" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8541" spans="1:4">
+      <c r="A8541" t="s">
+        <v>8547</v>
+      </c>
+      <c r="D8541" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8542" spans="1:4">
+      <c r="A8542" t="s">
+        <v>8548</v>
+      </c>
+      <c r="D8542" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17089" uniqueCount="8549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17107" uniqueCount="8558">
   <si>
     <t>code</t>
   </si>
@@ -43,6 +43,30 @@
     <t>en</t>
   </si>
   <si>
+    <t>TC-2025-000170-CHN</t>
+  </si>
+  <si>
+    <t>TC-2025-000170-PHL</t>
+  </si>
+  <si>
+    <t>TC-2025-000170-TWN</t>
+  </si>
+  <si>
+    <t>TC-2025-000170-VNM</t>
+  </si>
+  <si>
+    <t>FL-2025-000169-SLE</t>
+  </si>
+  <si>
+    <t>FL-2025-000168-SSD</t>
+  </si>
+  <si>
+    <t>TC-2025-000167-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2025-000166-RUS</t>
+  </si>
+  <si>
     <t>LS-2025-000165-MYS</t>
   </si>
   <si>
@@ -554,6 +578,9 @@
   </si>
   <si>
     <t>EQ-2025-000001-ETH</t>
+  </si>
+  <si>
+    <t>FL-2024-000235-BEN</t>
   </si>
   <si>
     <t>DR-2024-000234-PNG</t>
@@ -25992,7 +26019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8542"/>
+  <dimension ref="A1:G8551"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94346,6 +94373,78 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8543" spans="1:4">
+      <c r="A8543" t="s">
+        <v>8549</v>
+      </c>
+      <c r="D8543" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8544" spans="1:4">
+      <c r="A8544" t="s">
+        <v>8550</v>
+      </c>
+      <c r="D8544" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8545" spans="1:4">
+      <c r="A8545" t="s">
+        <v>8551</v>
+      </c>
+      <c r="D8545" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8546" spans="1:4">
+      <c r="A8546" t="s">
+        <v>8552</v>
+      </c>
+      <c r="D8546" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8547" spans="1:4">
+      <c r="A8547" t="s">
+        <v>8553</v>
+      </c>
+      <c r="D8547" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8548" spans="1:4">
+      <c r="A8548" t="s">
+        <v>8554</v>
+      </c>
+      <c r="D8548" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8549" spans="1:4">
+      <c r="A8549" t="s">
+        <v>8555</v>
+      </c>
+      <c r="D8549" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8550" spans="1:4">
+      <c r="A8550" t="s">
+        <v>8556</v>
+      </c>
+      <c r="D8550" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8551" spans="1:4">
+      <c r="A8551" t="s">
+        <v>8557</v>
+      </c>
+      <c r="D8551" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17107" uniqueCount="8558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17121" uniqueCount="8565">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,27 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2025-000177-YEM</t>
+  </si>
+  <si>
+    <t>TC-2025-000176-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2025-000175-VEN</t>
+  </si>
+  <si>
+    <t>FL-2025-000174-HTI</t>
+  </si>
+  <si>
+    <t>EQ-2025-000173-VEN</t>
+  </si>
+  <si>
+    <t>DR-2025-000172-SOM</t>
+  </si>
+  <si>
+    <t>FL-2025-000171-IND</t>
   </si>
   <si>
     <t>TC-2025-000170-CHN</t>
@@ -26019,7 +26040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8551"/>
+  <dimension ref="A1:G8558"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94445,6 +94466,62 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8552" spans="1:4">
+      <c r="A8552" t="s">
+        <v>8558</v>
+      </c>
+      <c r="D8552" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8553" spans="1:4">
+      <c r="A8553" t="s">
+        <v>8559</v>
+      </c>
+      <c r="D8553" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8554" spans="1:4">
+      <c r="A8554" t="s">
+        <v>8560</v>
+      </c>
+      <c r="D8554" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8555" spans="1:4">
+      <c r="A8555" t="s">
+        <v>8561</v>
+      </c>
+      <c r="D8555" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8556" spans="1:4">
+      <c r="A8556" t="s">
+        <v>8562</v>
+      </c>
+      <c r="D8556" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8557" spans="1:4">
+      <c r="A8557" t="s">
+        <v>8563</v>
+      </c>
+      <c r="D8557" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8558" spans="1:4">
+      <c r="A8558" t="s">
+        <v>8564</v>
+      </c>
+      <c r="D8558" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17121" uniqueCount="8565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17143" uniqueCount="8576">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,39 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EQ-2025-000188-CHN</t>
+  </si>
+  <si>
+    <t>FL-2025-000187-NGA</t>
+  </si>
+  <si>
+    <t>TC-2025-000186-VNM</t>
+  </si>
+  <si>
+    <t>FF-2025-000185-GEO</t>
+  </si>
+  <si>
+    <t>FL-2025-000184-NPL</t>
+  </si>
+  <si>
+    <t>TC-2025-000183-VNM</t>
+  </si>
+  <si>
+    <t>EP-2025-000182-SOM</t>
+  </si>
+  <si>
+    <t>EQ-2025-000181-PHL</t>
+  </si>
+  <si>
+    <t>DR-2025-000180-CHN</t>
+  </si>
+  <si>
+    <t>TC-2025-000179-VNM</t>
+  </si>
+  <si>
+    <t>FL-2025-000178-CHN</t>
   </si>
   <si>
     <t>FL-2025-000177-YEM</t>
@@ -26040,7 +26073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8558"/>
+  <dimension ref="A1:G8569"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94522,6 +94555,94 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8559" spans="1:4">
+      <c r="A8559" t="s">
+        <v>8565</v>
+      </c>
+      <c r="D8559" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8560" spans="1:4">
+      <c r="A8560" t="s">
+        <v>8566</v>
+      </c>
+      <c r="D8560" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8561" spans="1:4">
+      <c r="A8561" t="s">
+        <v>8567</v>
+      </c>
+      <c r="D8561" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8562" spans="1:4">
+      <c r="A8562" t="s">
+        <v>8568</v>
+      </c>
+      <c r="D8562" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8563" spans="1:4">
+      <c r="A8563" t="s">
+        <v>8569</v>
+      </c>
+      <c r="D8563" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8564" spans="1:4">
+      <c r="A8564" t="s">
+        <v>8570</v>
+      </c>
+      <c r="D8564" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8565" spans="1:4">
+      <c r="A8565" t="s">
+        <v>8571</v>
+      </c>
+      <c r="D8565" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8566" spans="1:4">
+      <c r="A8566" t="s">
+        <v>8572</v>
+      </c>
+      <c r="D8566" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8567" spans="1:4">
+      <c r="A8567" t="s">
+        <v>8573</v>
+      </c>
+      <c r="D8567" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8568" spans="1:4">
+      <c r="A8568" t="s">
+        <v>8574</v>
+      </c>
+      <c r="D8568" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8569" spans="1:4">
+      <c r="A8569" t="s">
+        <v>8575</v>
+      </c>
+      <c r="D8569" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17143" uniqueCount="8576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17153" uniqueCount="8581">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,21 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2025-000193-MEX</t>
+  </si>
+  <si>
+    <t>EQ-2025-000192-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2025-000191-ETH</t>
+  </si>
+  <si>
+    <t>FL-2025-000190-EGY</t>
+  </si>
+  <si>
+    <t>EQ-2025-000189-PHL</t>
   </si>
   <si>
     <t>EQ-2025-000188-CHN</t>
@@ -26073,7 +26088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8569"/>
+  <dimension ref="A1:G8574"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94643,6 +94658,46 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8570" spans="1:4">
+      <c r="A8570" t="s">
+        <v>8576</v>
+      </c>
+      <c r="D8570" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8571" spans="1:4">
+      <c r="A8571" t="s">
+        <v>8577</v>
+      </c>
+      <c r="D8571" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8572" spans="1:4">
+      <c r="A8572" t="s">
+        <v>8578</v>
+      </c>
+      <c r="D8572" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8573" spans="1:4">
+      <c r="A8573" t="s">
+        <v>8579</v>
+      </c>
+      <c r="D8573" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8574" spans="1:4">
+      <c r="A8574" t="s">
+        <v>8580</v>
+      </c>
+      <c r="D8574" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17153" uniqueCount="8581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17161" uniqueCount="8585">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,18 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2025-000196-HTI</t>
+  </si>
+  <si>
+    <t>TC-2025-000195-PHL</t>
+  </si>
+  <si>
+    <t>TC-2025-000195-VNM</t>
+  </si>
+  <si>
+    <t>VO-2025-000194-IDN</t>
   </si>
   <si>
     <t>FL-2025-000193-MEX</t>
@@ -26088,7 +26100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8574"/>
+  <dimension ref="A1:G8578"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94698,6 +94710,38 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8575" spans="1:4">
+      <c r="A8575" t="s">
+        <v>8581</v>
+      </c>
+      <c r="D8575" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8576" spans="1:4">
+      <c r="A8576" t="s">
+        <v>8582</v>
+      </c>
+      <c r="D8576" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8577" spans="1:4">
+      <c r="A8577" t="s">
+        <v>8583</v>
+      </c>
+      <c r="D8577" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8578" spans="1:4">
+      <c r="A8578" t="s">
+        <v>8584</v>
+      </c>
+      <c r="D8578" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17161" uniqueCount="8585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17175" uniqueCount="8592">
   <si>
     <t>code</t>
   </si>
@@ -43,7 +43,28 @@
     <t>en</t>
   </si>
   <si>
+    <t>EQ-2025-000202-AFG</t>
+  </si>
+  <si>
+    <t>FL-2025-000201-CUB</t>
+  </si>
+  <si>
+    <t>EP-2025-000200-CUB</t>
+  </si>
+  <si>
+    <t>AV-2025-000199-TJK</t>
+  </si>
+  <si>
+    <t>FL-2025-000198-VNM</t>
+  </si>
+  <si>
+    <t>EQ-2025-000197-TUR</t>
+  </si>
+  <si>
     <t>TC-2025-000196-HTI</t>
+  </si>
+  <si>
+    <t>TC-2025-000196-JAM</t>
   </si>
   <si>
     <t>TC-2025-000195-PHL</t>
@@ -26100,7 +26121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8578"/>
+  <dimension ref="A1:G8585"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94742,6 +94763,62 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8579" spans="1:4">
+      <c r="A8579" t="s">
+        <v>8585</v>
+      </c>
+      <c r="D8579" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8580" spans="1:4">
+      <c r="A8580" t="s">
+        <v>8586</v>
+      </c>
+      <c r="D8580" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8581" spans="1:4">
+      <c r="A8581" t="s">
+        <v>8587</v>
+      </c>
+      <c r="D8581" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8582" spans="1:4">
+      <c r="A8582" t="s">
+        <v>8588</v>
+      </c>
+      <c r="D8582" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8583" spans="1:4">
+      <c r="A8583" t="s">
+        <v>8589</v>
+      </c>
+      <c r="D8583" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8584" spans="1:4">
+      <c r="A8584" t="s">
+        <v>8590</v>
+      </c>
+      <c r="D8584" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8585" spans="1:4">
+      <c r="A8585" t="s">
+        <v>8591</v>
+      </c>
+      <c r="D8585" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17175" uniqueCount="8592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17177" uniqueCount="8593">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2025-000203-PHL</t>
   </si>
   <si>
     <t>EQ-2025-000202-AFG</t>
@@ -26121,7 +26124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8585"/>
+  <dimension ref="A1:G8586"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94819,6 +94822,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8586" spans="1:4">
+      <c r="A8586" t="s">
+        <v>8592</v>
+      </c>
+      <c r="D8586" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17177" uniqueCount="8593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17289" uniqueCount="8649">
   <si>
     <t>code</t>
   </si>
@@ -43,9 +43,111 @@
     <t>en</t>
   </si>
   <si>
+    <t>FL-2026-000006-TUN</t>
+  </si>
+  <si>
+    <t>FL-2026-000005-MKD</t>
+  </si>
+  <si>
+    <t>FL-2026-000004-MOZ</t>
+  </si>
+  <si>
+    <t>WF-2026-000003-CHL</t>
+  </si>
+  <si>
+    <t>CW-2026-000002-SRB</t>
+  </si>
+  <si>
+    <t>FL-2026-000001-MYS</t>
+  </si>
+  <si>
+    <t>EP-2025-000230-MDG</t>
+  </si>
+  <si>
+    <t>FL-2025-000229-CMR</t>
+  </si>
+  <si>
+    <t>FL-2025-000228-MOZ</t>
+  </si>
+  <si>
+    <t>FL-2025-000227-MOZ</t>
+  </si>
+  <si>
+    <t>CW-2025-000226-SYR</t>
+  </si>
+  <si>
+    <t>FF-2025-000225-IRN</t>
+  </si>
+  <si>
+    <t>FL-2025-000224-PSE</t>
+  </si>
+  <si>
+    <t>FF-2025-000223-MAR</t>
+  </si>
+  <si>
+    <t>FF-2025-000222-IRQ</t>
+  </si>
+  <si>
+    <t>WF-2025-000221-IRN</t>
+  </si>
+  <si>
+    <t>EQ-2025-000220-JPN</t>
+  </si>
+  <si>
+    <t>FL-2025-000219-COG</t>
+  </si>
+  <si>
+    <t>TC-2025-000218-LKA</t>
+  </si>
+  <si>
+    <t>FL-2025-000217-IDN</t>
+  </si>
+  <si>
+    <t>FL-2025-000216-LKA</t>
+  </si>
+  <si>
+    <t>EP-2025-000215-ETH</t>
+  </si>
+  <si>
+    <t>FL-2025-000213-LKA</t>
+  </si>
+  <si>
+    <t>LS-2025-000212-IDN</t>
+  </si>
+  <si>
+    <t>FL-2025-000211-MYS</t>
+  </si>
+  <si>
+    <t>FL-2025-000210-THA</t>
+  </si>
+  <si>
+    <t>FL-2025-000209-THA</t>
+  </si>
+  <si>
+    <t>EQ-2025-000208-BGD</t>
+  </si>
+  <si>
+    <t>FL-2025-000207-VNM</t>
+  </si>
+  <si>
+    <t>VO-2025-000206-IDN</t>
+  </si>
+  <si>
+    <t>LS-2025-000205-IDN</t>
+  </si>
+  <si>
+    <t>TC-2025-000204-PHL</t>
+  </si>
+  <si>
+    <t>TC-2025-000204-TWN</t>
+  </si>
+  <si>
     <t>TC-2025-000203-PHL</t>
   </si>
   <si>
+    <t>TC-2025-000203-VNM</t>
+  </si>
+  <si>
     <t>EQ-2025-000202-AFG</t>
   </si>
   <si>
@@ -683,6 +785,72 @@
   </si>
   <si>
     <t>EQ-2025-000001-ETH</t>
+  </si>
+  <si>
+    <t>TO-2024-000257-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000256-USA</t>
+  </si>
+  <si>
+    <t>DR-2024-000255-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000254-USA</t>
+  </si>
+  <si>
+    <t>CW-2024-000253-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000252-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000251-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000250-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000249-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000248-USA</t>
+  </si>
+  <si>
+    <t>TC-2024-000247-USA</t>
+  </si>
+  <si>
+    <t>TC-2024-000246-USA</t>
+  </si>
+  <si>
+    <t>TO-2024-000245-USA</t>
+  </si>
+  <si>
+    <t>TC-2024-000244-USA</t>
+  </si>
+  <si>
+    <t>WF-2024-000243-USA</t>
+  </si>
+  <si>
+    <t>TO-2024-000242-USA</t>
+  </si>
+  <si>
+    <t>TO-2024-000241-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000240-USA</t>
+  </si>
+  <si>
+    <t>TO-2024-000239-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000238-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000237-USA</t>
+  </si>
+  <si>
+    <t>TO-2024-000236-USA</t>
   </si>
   <si>
     <t>FL-2024-000235-BEN</t>
@@ -26124,7 +26292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8586"/>
+  <dimension ref="A1:G8642"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94830,6 +94998,454 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8587" spans="1:4">
+      <c r="A8587" t="s">
+        <v>8593</v>
+      </c>
+      <c r="D8587" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8588" spans="1:4">
+      <c r="A8588" t="s">
+        <v>8594</v>
+      </c>
+      <c r="D8588" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8589" spans="1:4">
+      <c r="A8589" t="s">
+        <v>8595</v>
+      </c>
+      <c r="D8589" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8590" spans="1:4">
+      <c r="A8590" t="s">
+        <v>8596</v>
+      </c>
+      <c r="D8590" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8591" spans="1:4">
+      <c r="A8591" t="s">
+        <v>8597</v>
+      </c>
+      <c r="D8591" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8592" spans="1:4">
+      <c r="A8592" t="s">
+        <v>8598</v>
+      </c>
+      <c r="D8592" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8593" spans="1:4">
+      <c r="A8593" t="s">
+        <v>8599</v>
+      </c>
+      <c r="D8593" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8594" spans="1:4">
+      <c r="A8594" t="s">
+        <v>8600</v>
+      </c>
+      <c r="D8594" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8595" spans="1:4">
+      <c r="A8595" t="s">
+        <v>8601</v>
+      </c>
+      <c r="D8595" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8596" spans="1:4">
+      <c r="A8596" t="s">
+        <v>8602</v>
+      </c>
+      <c r="D8596" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8597" spans="1:4">
+      <c r="A8597" t="s">
+        <v>8603</v>
+      </c>
+      <c r="D8597" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8598" spans="1:4">
+      <c r="A8598" t="s">
+        <v>8604</v>
+      </c>
+      <c r="D8598" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8599" spans="1:4">
+      <c r="A8599" t="s">
+        <v>8605</v>
+      </c>
+      <c r="D8599" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8600" spans="1:4">
+      <c r="A8600" t="s">
+        <v>8606</v>
+      </c>
+      <c r="D8600" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8601" spans="1:4">
+      <c r="A8601" t="s">
+        <v>8607</v>
+      </c>
+      <c r="D8601" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8602" spans="1:4">
+      <c r="A8602" t="s">
+        <v>8608</v>
+      </c>
+      <c r="D8602" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8603" spans="1:4">
+      <c r="A8603" t="s">
+        <v>8609</v>
+      </c>
+      <c r="D8603" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8604" spans="1:4">
+      <c r="A8604" t="s">
+        <v>8610</v>
+      </c>
+      <c r="D8604" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8605" spans="1:4">
+      <c r="A8605" t="s">
+        <v>8611</v>
+      </c>
+      <c r="D8605" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8606" spans="1:4">
+      <c r="A8606" t="s">
+        <v>8612</v>
+      </c>
+      <c r="D8606" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8607" spans="1:4">
+      <c r="A8607" t="s">
+        <v>8613</v>
+      </c>
+      <c r="D8607" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8608" spans="1:4">
+      <c r="A8608" t="s">
+        <v>8614</v>
+      </c>
+      <c r="D8608" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8609" spans="1:4">
+      <c r="A8609" t="s">
+        <v>8615</v>
+      </c>
+      <c r="D8609" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8610" spans="1:4">
+      <c r="A8610" t="s">
+        <v>8616</v>
+      </c>
+      <c r="D8610" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8611" spans="1:4">
+      <c r="A8611" t="s">
+        <v>8617</v>
+      </c>
+      <c r="D8611" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8612" spans="1:4">
+      <c r="A8612" t="s">
+        <v>8618</v>
+      </c>
+      <c r="D8612" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8613" spans="1:4">
+      <c r="A8613" t="s">
+        <v>8619</v>
+      </c>
+      <c r="D8613" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8614" spans="1:4">
+      <c r="A8614" t="s">
+        <v>8620</v>
+      </c>
+      <c r="D8614" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8615" spans="1:4">
+      <c r="A8615" t="s">
+        <v>8621</v>
+      </c>
+      <c r="D8615" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8616" spans="1:4">
+      <c r="A8616" t="s">
+        <v>8622</v>
+      </c>
+      <c r="D8616" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8617" spans="1:4">
+      <c r="A8617" t="s">
+        <v>8623</v>
+      </c>
+      <c r="D8617" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8618" spans="1:4">
+      <c r="A8618" t="s">
+        <v>8624</v>
+      </c>
+      <c r="D8618" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8619" spans="1:4">
+      <c r="A8619" t="s">
+        <v>8625</v>
+      </c>
+      <c r="D8619" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8620" spans="1:4">
+      <c r="A8620" t="s">
+        <v>8626</v>
+      </c>
+      <c r="D8620" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8621" spans="1:4">
+      <c r="A8621" t="s">
+        <v>8627</v>
+      </c>
+      <c r="D8621" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8622" spans="1:4">
+      <c r="A8622" t="s">
+        <v>8628</v>
+      </c>
+      <c r="D8622" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8623" spans="1:4">
+      <c r="A8623" t="s">
+        <v>8629</v>
+      </c>
+      <c r="D8623" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8624" spans="1:4">
+      <c r="A8624" t="s">
+        <v>8630</v>
+      </c>
+      <c r="D8624" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8625" spans="1:4">
+      <c r="A8625" t="s">
+        <v>8631</v>
+      </c>
+      <c r="D8625" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8626" spans="1:4">
+      <c r="A8626" t="s">
+        <v>8632</v>
+      </c>
+      <c r="D8626" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8627" spans="1:4">
+      <c r="A8627" t="s">
+        <v>8633</v>
+      </c>
+      <c r="D8627" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8628" spans="1:4">
+      <c r="A8628" t="s">
+        <v>8634</v>
+      </c>
+      <c r="D8628" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8629" spans="1:4">
+      <c r="A8629" t="s">
+        <v>8635</v>
+      </c>
+      <c r="D8629" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8630" spans="1:4">
+      <c r="A8630" t="s">
+        <v>8636</v>
+      </c>
+      <c r="D8630" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8631" spans="1:4">
+      <c r="A8631" t="s">
+        <v>8637</v>
+      </c>
+      <c r="D8631" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8632" spans="1:4">
+      <c r="A8632" t="s">
+        <v>8638</v>
+      </c>
+      <c r="D8632" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8633" spans="1:4">
+      <c r="A8633" t="s">
+        <v>8639</v>
+      </c>
+      <c r="D8633" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8634" spans="1:4">
+      <c r="A8634" t="s">
+        <v>8640</v>
+      </c>
+      <c r="D8634" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8635" spans="1:4">
+      <c r="A8635" t="s">
+        <v>8641</v>
+      </c>
+      <c r="D8635" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8636" spans="1:4">
+      <c r="A8636" t="s">
+        <v>8642</v>
+      </c>
+      <c r="D8636" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8637" spans="1:4">
+      <c r="A8637" t="s">
+        <v>8643</v>
+      </c>
+      <c r="D8637" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8638" spans="1:4">
+      <c r="A8638" t="s">
+        <v>8644</v>
+      </c>
+      <c r="D8638" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8639" spans="1:4">
+      <c r="A8639" t="s">
+        <v>8645</v>
+      </c>
+      <c r="D8639" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8640" spans="1:4">
+      <c r="A8640" t="s">
+        <v>8646</v>
+      </c>
+      <c r="D8640" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8641" spans="1:4">
+      <c r="A8641" t="s">
+        <v>8647</v>
+      </c>
+      <c r="D8641" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8642" spans="1:4">
+      <c r="A8642" t="s">
+        <v>8648</v>
+      </c>
+      <c r="D8642" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17289" uniqueCount="8649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17561" uniqueCount="8785">
   <si>
     <t>code</t>
   </si>
@@ -43,6 +43,360 @@
     <t>en</t>
   </si>
   <si>
+    <t>FL-2026-000114-KGZ</t>
+  </si>
+  <si>
+    <t>WF-2026-000113-ESP</t>
+  </si>
+  <si>
+    <t>WF-2026-000112-FRA</t>
+  </si>
+  <si>
+    <t>FL-2026-000111-TJK</t>
+  </si>
+  <si>
+    <t>FL-2026-000110-BGD</t>
+  </si>
+  <si>
+    <t>FL-2026-000109-BGD</t>
+  </si>
+  <si>
+    <t>LS-2026-000108-CHN</t>
+  </si>
+  <si>
+    <t>EP-2026-000107-CAF</t>
+  </si>
+  <si>
+    <t>FL-2026-000106-GEO</t>
+  </si>
+  <si>
+    <t>FL-2026-000105-CHN</t>
+  </si>
+  <si>
+    <t>LS-2026-000104-KGZ</t>
+  </si>
+  <si>
+    <t>OT-2026-000103-KGZ</t>
+  </si>
+  <si>
+    <t>WF-2026-000102-FRA</t>
+  </si>
+  <si>
+    <t>WF-2026-000101-PRT</t>
+  </si>
+  <si>
+    <t>FL-2026-000100-KAZ</t>
+  </si>
+  <si>
+    <t>LS-2026-000099-PHL</t>
+  </si>
+  <si>
+    <t>TC-2026-000099-CHN</t>
+  </si>
+  <si>
+    <t>TC-2026-000099-GUM</t>
+  </si>
+  <si>
+    <t>TC-2026-000099-TWN</t>
+  </si>
+  <si>
+    <t>TC-2026-000098-CHN</t>
+  </si>
+  <si>
+    <t>TC-2026-000098-VNM</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-CHE</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-DEU</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-ESP</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-FRA</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-GBR</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-NLD</t>
+  </si>
+  <si>
+    <t>EQ-2026-000096-JPN</t>
+  </si>
+  <si>
+    <t>EP-2026-000095-IRQ</t>
+  </si>
+  <si>
+    <t>EQ-2026-000094-JPN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000093-VEN</t>
+  </si>
+  <si>
+    <t>LS-2026-000092-JPN</t>
+  </si>
+  <si>
+    <t>FL-2026-000091-MDA</t>
+  </si>
+  <si>
+    <t>TC-2026-000090-JPN</t>
+  </si>
+  <si>
+    <t>TC-2026-000090-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2026-000089-IDN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000088-CHN</t>
+  </si>
+  <si>
+    <t>FL-2026-000087-DOM</t>
+  </si>
+  <si>
+    <t>ST-2026-000086-ARM</t>
+  </si>
+  <si>
+    <t>EP-2026-000085-LKA</t>
+  </si>
+  <si>
+    <t>EQ-2026-000084-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2026-000083-IDN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000083-PHL</t>
+  </si>
+  <si>
+    <t>OT-2026-000082-KGZ</t>
+  </si>
+  <si>
+    <t>LS-2026-000081-KGZ</t>
+  </si>
+  <si>
+    <t>FL-2026-000080-SYR</t>
+  </si>
+  <si>
+    <t>EP-2026-000079-SLE</t>
+  </si>
+  <si>
+    <t>TC-2026-000078-JPN</t>
+  </si>
+  <si>
+    <t>TC-2026-000078-PHL</t>
+  </si>
+  <si>
+    <t>FL-2026-000077-UZB</t>
+  </si>
+  <si>
+    <t>FL-2026-000076-KGZ</t>
+  </si>
+  <si>
+    <t>FL-2026-000075-CHN</t>
+  </si>
+  <si>
+    <t>FF-2026-000074-AFG</t>
+  </si>
+  <si>
+    <t>EQ-2026-000073-CHN</t>
+  </si>
+  <si>
+    <t>ST-2026-000072-IND</t>
+  </si>
+  <si>
+    <t>EP-2026-000071-COD</t>
+  </si>
+  <si>
+    <t>FL-2026-000069-KEN</t>
+  </si>
+  <si>
+    <t>VO-2026-000068-IDN</t>
+  </si>
+  <si>
+    <t>FL-2026-000067-TJK</t>
+  </si>
+  <si>
+    <t>FL-2026-000066-KGZ</t>
+  </si>
+  <si>
+    <t>VO-2026-000065-PHL</t>
+  </si>
+  <si>
+    <t>FR-2026-000064-MYS</t>
+  </si>
+  <si>
+    <t>FL-2026-000063-TZA</t>
+  </si>
+  <si>
+    <t>ST-2026-000062-VNM</t>
+  </si>
+  <si>
+    <t>ST-2026-000061-THA</t>
+  </si>
+  <si>
+    <t>WF-2026-000060-JPN</t>
+  </si>
+  <si>
+    <t>FL-2026-000059-NZL</t>
+  </si>
+  <si>
+    <t>FL-2026-000058-HTI</t>
+  </si>
+  <si>
+    <t>EQ-2026-000057-JPN</t>
+  </si>
+  <si>
+    <t>FL-2026-000056-CAN</t>
+  </si>
+  <si>
+    <t>FR-2026-000055-GNB</t>
+  </si>
+  <si>
+    <t>VW-2026-000054-LBR</t>
+  </si>
+  <si>
+    <t>TC-2026-000053-FJI</t>
+  </si>
+  <si>
+    <t>FR-2026-000052-LBR</t>
+  </si>
+  <si>
+    <t>TC-2026-000051-PNG</t>
+  </si>
+  <si>
+    <t>TC-2026-000051-SLB</t>
+  </si>
+  <si>
+    <t>TC-2026-000050-FSM</t>
+  </si>
+  <si>
+    <t>EP-2026-000048-BGD</t>
+  </si>
+  <si>
+    <t>FL-2026-000047-AFG</t>
+  </si>
+  <si>
+    <t>FL-2026-000046-BWA</t>
+  </si>
+  <si>
+    <t>FL-2026-000045-KAZ</t>
+  </si>
+  <si>
+    <t>FL-2026-000044-YEM</t>
+  </si>
+  <si>
+    <t>FF-2026-000043-AFG</t>
+  </si>
+  <si>
+    <t>EQ-2026-000042-VUT</t>
+  </si>
+  <si>
+    <t>LS-2026-000041-ARG</t>
+  </si>
+  <si>
+    <t>FL-2026-000040-RWA</t>
+  </si>
+  <si>
+    <t>EP-2026-000039-SOM</t>
+  </si>
+  <si>
+    <t>FL-2026-000038-PER</t>
+  </si>
+  <si>
+    <t>EP-2026-000037-SUR</t>
+  </si>
+  <si>
+    <t>FL-2026-000036-AGO</t>
+  </si>
+  <si>
+    <t>VO-2026-000035-VUT</t>
+  </si>
+  <si>
+    <t>VO-2026-000034-PHL</t>
+  </si>
+  <si>
+    <t>FL-2026-000033-ETH</t>
+  </si>
+  <si>
+    <t>CE-2026-000032-AFG</t>
+  </si>
+  <si>
+    <t>OT-2026-000031-CMR</t>
+  </si>
+  <si>
+    <t>FL-2026-000030-COD</t>
+  </si>
+  <si>
+    <t>EP-2026-000029-ZMB</t>
+  </si>
+  <si>
+    <t>FL-2026-000028-BRA</t>
+  </si>
+  <si>
+    <t>FL-2026-000027-ECU</t>
+  </si>
+  <si>
+    <t>CE-2026-000026-IRN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000025-BGD</t>
+  </si>
+  <si>
+    <t>CW-2026-000024-MNG</t>
+  </si>
+  <si>
+    <t>FL-2026-000023-ZWE</t>
+  </si>
+  <si>
+    <t>FR-2026-000022-CMR</t>
+  </si>
+  <si>
+    <t>FL-2026-000021-MWI</t>
+  </si>
+  <si>
+    <t>FL-2026-000020-ZMB</t>
+  </si>
+  <si>
+    <t>OT-2026-000019-LBN</t>
+  </si>
+  <si>
+    <t>FL-2026-000018-SYR</t>
+  </si>
+  <si>
+    <t>FL-2026-000017-COL</t>
+  </si>
+  <si>
+    <t>TC-2026-000015-MDG</t>
+  </si>
+  <si>
+    <t>EP-2026-000014-COM</t>
+  </si>
+  <si>
+    <t>CW-2026-000013-JPN</t>
+  </si>
+  <si>
+    <t>EP-2026-000012-GTM</t>
+  </si>
+  <si>
+    <t>FL-2026-000011-ZAF</t>
+  </si>
+  <si>
+    <t>FL-2026-000010-COD</t>
+  </si>
+  <si>
+    <t>TC-2026-000009-MDG</t>
+  </si>
+  <si>
+    <t>FL-2026-000008-DZA</t>
+  </si>
+  <si>
+    <t>LS-2026-000007-IDN</t>
+  </si>
+  <si>
     <t>FL-2026-000006-TUN</t>
   </si>
   <si>
@@ -61,6 +415,30 @@
     <t>FL-2026-000001-MYS</t>
   </si>
   <si>
+    <t>DR-2025-000238-MDG</t>
+  </si>
+  <si>
+    <t>FL-2025-000237-COD</t>
+  </si>
+  <si>
+    <t>DR-2025-000236-ARG</t>
+  </si>
+  <si>
+    <t>FL-2025-000235-BOL</t>
+  </si>
+  <si>
+    <t>DR-2025-000234-AGO</t>
+  </si>
+  <si>
+    <t>FL-2025-000233-IDN</t>
+  </si>
+  <si>
+    <t>EP-2025-000232-COK</t>
+  </si>
+  <si>
+    <t>ST-2025-000231-GAB</t>
+  </si>
+  <si>
     <t>EP-2025-000230-MDG</t>
   </si>
   <si>
@@ -1603,6 +1981,9 @@
     <t>EQ-2024-000001-JPN</t>
   </si>
   <si>
+    <t>FL-2023-000290-LBY</t>
+  </si>
+  <si>
     <t>TC-2023-000289-GUM</t>
   </si>
   <si>
@@ -3274,6 +3655,12 @@
     <t>EQ-2022-000001-CHN</t>
   </si>
   <si>
+    <t>TC-2021-000233-VNM</t>
+  </si>
+  <si>
+    <t>TC-2021-000232-MEX</t>
+  </si>
+  <si>
     <t>ST-2021-000231-KHM</t>
   </si>
   <si>
@@ -5065,6 +5452,12 @@
     <t>EQ-2020-000001-PRI</t>
   </si>
   <si>
+    <t>TC-2019-000202-IND</t>
+  </si>
+  <si>
+    <t>FL-2019-000201-MOZ</t>
+  </si>
+  <si>
     <t>AC-2019-000200-KHM</t>
   </si>
   <si>
@@ -5656,6 +6049,12 @@
     <t>TC-2019-000001-THA</t>
   </si>
   <si>
+    <t>FL-2018-000443-IND</t>
+  </si>
+  <si>
+    <t>FL-2018-000442-NGA</t>
+  </si>
+  <si>
     <t>CW-2018-000441-USA</t>
   </si>
   <si>
@@ -6194,6 +6593,15 @@
   </si>
   <si>
     <t>TC-2018-000001-MDG</t>
+  </si>
+  <si>
+    <t>FL-2017-000204-MDG</t>
+  </si>
+  <si>
+    <t>FL-2017-000203-BGD</t>
+  </si>
+  <si>
+    <t>FL-2017-000202-SLE</t>
   </si>
   <si>
     <t>ST-2017-000199-USA</t>
@@ -26292,7 +26700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8642"/>
+  <dimension ref="A1:G8778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -95446,6 +95854,1094 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8643" spans="1:4">
+      <c r="A8643" t="s">
+        <v>8649</v>
+      </c>
+      <c r="D8643" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8644" spans="1:4">
+      <c r="A8644" t="s">
+        <v>8650</v>
+      </c>
+      <c r="D8644" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8645" spans="1:4">
+      <c r="A8645" t="s">
+        <v>8651</v>
+      </c>
+      <c r="D8645" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8646" spans="1:4">
+      <c r="A8646" t="s">
+        <v>8652</v>
+      </c>
+      <c r="D8646" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8647" spans="1:4">
+      <c r="A8647" t="s">
+        <v>8653</v>
+      </c>
+      <c r="D8647" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8648" spans="1:4">
+      <c r="A8648" t="s">
+        <v>8654</v>
+      </c>
+      <c r="D8648" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8649" spans="1:4">
+      <c r="A8649" t="s">
+        <v>8655</v>
+      </c>
+      <c r="D8649" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8650" spans="1:4">
+      <c r="A8650" t="s">
+        <v>8656</v>
+      </c>
+      <c r="D8650" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8651" spans="1:4">
+      <c r="A8651" t="s">
+        <v>8657</v>
+      </c>
+      <c r="D8651" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8652" spans="1:4">
+      <c r="A8652" t="s">
+        <v>8658</v>
+      </c>
+      <c r="D8652" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8653" spans="1:4">
+      <c r="A8653" t="s">
+        <v>8659</v>
+      </c>
+      <c r="D8653" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8654" spans="1:4">
+      <c r="A8654" t="s">
+        <v>8660</v>
+      </c>
+      <c r="D8654" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8655" spans="1:4">
+      <c r="A8655" t="s">
+        <v>8661</v>
+      </c>
+      <c r="D8655" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8656" spans="1:4">
+      <c r="A8656" t="s">
+        <v>8662</v>
+      </c>
+      <c r="D8656" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8657" spans="1:4">
+      <c r="A8657" t="s">
+        <v>8663</v>
+      </c>
+      <c r="D8657" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8658" spans="1:4">
+      <c r="A8658" t="s">
+        <v>8664</v>
+      </c>
+      <c r="D8658" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8659" spans="1:4">
+      <c r="A8659" t="s">
+        <v>8665</v>
+      </c>
+      <c r="D8659" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8660" spans="1:4">
+      <c r="A8660" t="s">
+        <v>8666</v>
+      </c>
+      <c r="D8660" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8661" spans="1:4">
+      <c r="A8661" t="s">
+        <v>8667</v>
+      </c>
+      <c r="D8661" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8662" spans="1:4">
+      <c r="A8662" t="s">
+        <v>8668</v>
+      </c>
+      <c r="D8662" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8663" spans="1:4">
+      <c r="A8663" t="s">
+        <v>8669</v>
+      </c>
+      <c r="D8663" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8664" spans="1:4">
+      <c r="A8664" t="s">
+        <v>8670</v>
+      </c>
+      <c r="D8664" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8665" spans="1:4">
+      <c r="A8665" t="s">
+        <v>8671</v>
+      </c>
+      <c r="D8665" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8666" spans="1:4">
+      <c r="A8666" t="s">
+        <v>8672</v>
+      </c>
+      <c r="D8666" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8667" spans="1:4">
+      <c r="A8667" t="s">
+        <v>8673</v>
+      </c>
+      <c r="D8667" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8668" spans="1:4">
+      <c r="A8668" t="s">
+        <v>8674</v>
+      </c>
+      <c r="D8668" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8669" spans="1:4">
+      <c r="A8669" t="s">
+        <v>8675</v>
+      </c>
+      <c r="D8669" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8670" spans="1:4">
+      <c r="A8670" t="s">
+        <v>8676</v>
+      </c>
+      <c r="D8670" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8671" spans="1:4">
+      <c r="A8671" t="s">
+        <v>8677</v>
+      </c>
+      <c r="D8671" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8672" spans="1:4">
+      <c r="A8672" t="s">
+        <v>8678</v>
+      </c>
+      <c r="D8672" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8673" spans="1:4">
+      <c r="A8673" t="s">
+        <v>8679</v>
+      </c>
+      <c r="D8673" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8674" spans="1:4">
+      <c r="A8674" t="s">
+        <v>8680</v>
+      </c>
+      <c r="D8674" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8675" spans="1:4">
+      <c r="A8675" t="s">
+        <v>8681</v>
+      </c>
+      <c r="D8675" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8676" spans="1:4">
+      <c r="A8676" t="s">
+        <v>8682</v>
+      </c>
+      <c r="D8676" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8677" spans="1:4">
+      <c r="A8677" t="s">
+        <v>8683</v>
+      </c>
+      <c r="D8677" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8678" spans="1:4">
+      <c r="A8678" t="s">
+        <v>8684</v>
+      </c>
+      <c r="D8678" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8679" spans="1:4">
+      <c r="A8679" t="s">
+        <v>8685</v>
+      </c>
+      <c r="D8679" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8680" spans="1:4">
+      <c r="A8680" t="s">
+        <v>8686</v>
+      </c>
+      <c r="D8680" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8681" spans="1:4">
+      <c r="A8681" t="s">
+        <v>8687</v>
+      </c>
+      <c r="D8681" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8682" spans="1:4">
+      <c r="A8682" t="s">
+        <v>8688</v>
+      </c>
+      <c r="D8682" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8683" spans="1:4">
+      <c r="A8683" t="s">
+        <v>8689</v>
+      </c>
+      <c r="D8683" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8684" spans="1:4">
+      <c r="A8684" t="s">
+        <v>8690</v>
+      </c>
+      <c r="D8684" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8685" spans="1:4">
+      <c r="A8685" t="s">
+        <v>8691</v>
+      </c>
+      <c r="D8685" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8686" spans="1:4">
+      <c r="A8686" t="s">
+        <v>8692</v>
+      </c>
+      <c r="D8686" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8687" spans="1:4">
+      <c r="A8687" t="s">
+        <v>8693</v>
+      </c>
+      <c r="D8687" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8688" spans="1:4">
+      <c r="A8688" t="s">
+        <v>8694</v>
+      </c>
+      <c r="D8688" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8689" spans="1:4">
+      <c r="A8689" t="s">
+        <v>8695</v>
+      </c>
+      <c r="D8689" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8690" spans="1:4">
+      <c r="A8690" t="s">
+        <v>8696</v>
+      </c>
+      <c r="D8690" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8691" spans="1:4">
+      <c r="A8691" t="s">
+        <v>8697</v>
+      </c>
+      <c r="D8691" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8692" spans="1:4">
+      <c r="A8692" t="s">
+        <v>8698</v>
+      </c>
+      <c r="D8692" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8693" spans="1:4">
+      <c r="A8693" t="s">
+        <v>8699</v>
+      </c>
+      <c r="D8693" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8694" spans="1:4">
+      <c r="A8694" t="s">
+        <v>8700</v>
+      </c>
+      <c r="D8694" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8695" spans="1:4">
+      <c r="A8695" t="s">
+        <v>8701</v>
+      </c>
+      <c r="D8695" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8696" spans="1:4">
+      <c r="A8696" t="s">
+        <v>8702</v>
+      </c>
+      <c r="D8696" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8697" spans="1:4">
+      <c r="A8697" t="s">
+        <v>8703</v>
+      </c>
+      <c r="D8697" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8698" spans="1:4">
+      <c r="A8698" t="s">
+        <v>8704</v>
+      </c>
+      <c r="D8698" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8699" spans="1:4">
+      <c r="A8699" t="s">
+        <v>8705</v>
+      </c>
+      <c r="D8699" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8700" spans="1:4">
+      <c r="A8700" t="s">
+        <v>8706</v>
+      </c>
+      <c r="D8700" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8701" spans="1:4">
+      <c r="A8701" t="s">
+        <v>8707</v>
+      </c>
+      <c r="D8701" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8702" spans="1:4">
+      <c r="A8702" t="s">
+        <v>8708</v>
+      </c>
+      <c r="D8702" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8703" spans="1:4">
+      <c r="A8703" t="s">
+        <v>8709</v>
+      </c>
+      <c r="D8703" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8704" spans="1:4">
+      <c r="A8704" t="s">
+        <v>8710</v>
+      </c>
+      <c r="D8704" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8705" spans="1:4">
+      <c r="A8705" t="s">
+        <v>8711</v>
+      </c>
+      <c r="D8705" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8706" spans="1:4">
+      <c r="A8706" t="s">
+        <v>8712</v>
+      </c>
+      <c r="D8706" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8707" spans="1:4">
+      <c r="A8707" t="s">
+        <v>8713</v>
+      </c>
+      <c r="D8707" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8708" spans="1:4">
+      <c r="A8708" t="s">
+        <v>8714</v>
+      </c>
+      <c r="D8708" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8709" spans="1:4">
+      <c r="A8709" t="s">
+        <v>8715</v>
+      </c>
+      <c r="D8709" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8710" spans="1:4">
+      <c r="A8710" t="s">
+        <v>8716</v>
+      </c>
+      <c r="D8710" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8711" spans="1:4">
+      <c r="A8711" t="s">
+        <v>8717</v>
+      </c>
+      <c r="D8711" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8712" spans="1:4">
+      <c r="A8712" t="s">
+        <v>8718</v>
+      </c>
+      <c r="D8712" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8713" spans="1:4">
+      <c r="A8713" t="s">
+        <v>8719</v>
+      </c>
+      <c r="D8713" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8714" spans="1:4">
+      <c r="A8714" t="s">
+        <v>8720</v>
+      </c>
+      <c r="D8714" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8715" spans="1:4">
+      <c r="A8715" t="s">
+        <v>8721</v>
+      </c>
+      <c r="D8715" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8716" spans="1:4">
+      <c r="A8716" t="s">
+        <v>8722</v>
+      </c>
+      <c r="D8716" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8717" spans="1:4">
+      <c r="A8717" t="s">
+        <v>8723</v>
+      </c>
+      <c r="D8717" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8718" spans="1:4">
+      <c r="A8718" t="s">
+        <v>8724</v>
+      </c>
+      <c r="D8718" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8719" spans="1:4">
+      <c r="A8719" t="s">
+        <v>8725</v>
+      </c>
+      <c r="D8719" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8720" spans="1:4">
+      <c r="A8720" t="s">
+        <v>8726</v>
+      </c>
+      <c r="D8720" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8721" spans="1:4">
+      <c r="A8721" t="s">
+        <v>8727</v>
+      </c>
+      <c r="D8721" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8722" spans="1:4">
+      <c r="A8722" t="s">
+        <v>8728</v>
+      </c>
+      <c r="D8722" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8723" spans="1:4">
+      <c r="A8723" t="s">
+        <v>8729</v>
+      </c>
+      <c r="D8723" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8724" spans="1:4">
+      <c r="A8724" t="s">
+        <v>8730</v>
+      </c>
+      <c r="D8724" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8725" spans="1:4">
+      <c r="A8725" t="s">
+        <v>8731</v>
+      </c>
+      <c r="D8725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8726" spans="1:4">
+      <c r="A8726" t="s">
+        <v>8732</v>
+      </c>
+      <c r="D8726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8727" spans="1:4">
+      <c r="A8727" t="s">
+        <v>8733</v>
+      </c>
+      <c r="D8727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8728" spans="1:4">
+      <c r="A8728" t="s">
+        <v>8734</v>
+      </c>
+      <c r="D8728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8729" spans="1:4">
+      <c r="A8729" t="s">
+        <v>8735</v>
+      </c>
+      <c r="D8729" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8730" spans="1:4">
+      <c r="A8730" t="s">
+        <v>8736</v>
+      </c>
+      <c r="D8730" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8731" spans="1:4">
+      <c r="A8731" t="s">
+        <v>8737</v>
+      </c>
+      <c r="D8731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8732" spans="1:4">
+      <c r="A8732" t="s">
+        <v>8738</v>
+      </c>
+      <c r="D8732" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8733" spans="1:4">
+      <c r="A8733" t="s">
+        <v>8739</v>
+      </c>
+      <c r="D8733" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8734" spans="1:4">
+      <c r="A8734" t="s">
+        <v>8740</v>
+      </c>
+      <c r="D8734" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8735" spans="1:4">
+      <c r="A8735" t="s">
+        <v>8741</v>
+      </c>
+      <c r="D8735" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8736" spans="1:4">
+      <c r="A8736" t="s">
+        <v>8742</v>
+      </c>
+      <c r="D8736" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8737" spans="1:4">
+      <c r="A8737" t="s">
+        <v>8743</v>
+      </c>
+      <c r="D8737" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8738" spans="1:4">
+      <c r="A8738" t="s">
+        <v>8744</v>
+      </c>
+      <c r="D8738" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8739" spans="1:4">
+      <c r="A8739" t="s">
+        <v>8745</v>
+      </c>
+      <c r="D8739" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8740" spans="1:4">
+      <c r="A8740" t="s">
+        <v>8746</v>
+      </c>
+      <c r="D8740" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8741" spans="1:4">
+      <c r="A8741" t="s">
+        <v>8747</v>
+      </c>
+      <c r="D8741" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8742" spans="1:4">
+      <c r="A8742" t="s">
+        <v>8748</v>
+      </c>
+      <c r="D8742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8743" spans="1:4">
+      <c r="A8743" t="s">
+        <v>8749</v>
+      </c>
+      <c r="D8743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8744" spans="1:4">
+      <c r="A8744" t="s">
+        <v>8750</v>
+      </c>
+      <c r="D8744" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8745" spans="1:4">
+      <c r="A8745" t="s">
+        <v>8751</v>
+      </c>
+      <c r="D8745" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8746" spans="1:4">
+      <c r="A8746" t="s">
+        <v>8752</v>
+      </c>
+      <c r="D8746" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8747" spans="1:4">
+      <c r="A8747" t="s">
+        <v>8753</v>
+      </c>
+      <c r="D8747" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8748" spans="1:4">
+      <c r="A8748" t="s">
+        <v>8754</v>
+      </c>
+      <c r="D8748" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8749" spans="1:4">
+      <c r="A8749" t="s">
+        <v>8755</v>
+      </c>
+      <c r="D8749" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8750" spans="1:4">
+      <c r="A8750" t="s">
+        <v>8756</v>
+      </c>
+      <c r="D8750" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8751" spans="1:4">
+      <c r="A8751" t="s">
+        <v>8757</v>
+      </c>
+      <c r="D8751" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8752" spans="1:4">
+      <c r="A8752" t="s">
+        <v>8758</v>
+      </c>
+      <c r="D8752" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8753" spans="1:4">
+      <c r="A8753" t="s">
+        <v>8759</v>
+      </c>
+      <c r="D8753" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8754" spans="1:4">
+      <c r="A8754" t="s">
+        <v>8760</v>
+      </c>
+      <c r="D8754" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8755" spans="1:4">
+      <c r="A8755" t="s">
+        <v>8761</v>
+      </c>
+      <c r="D8755" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8756" spans="1:4">
+      <c r="A8756" t="s">
+        <v>8762</v>
+      </c>
+      <c r="D8756" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8757" spans="1:4">
+      <c r="A8757" t="s">
+        <v>8763</v>
+      </c>
+      <c r="D8757" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8758" spans="1:4">
+      <c r="A8758" t="s">
+        <v>8764</v>
+      </c>
+      <c r="D8758" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8759" spans="1:4">
+      <c r="A8759" t="s">
+        <v>8765</v>
+      </c>
+      <c r="D8759" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8760" spans="1:4">
+      <c r="A8760" t="s">
+        <v>8766</v>
+      </c>
+      <c r="D8760" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8761" spans="1:4">
+      <c r="A8761" t="s">
+        <v>8767</v>
+      </c>
+      <c r="D8761" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8762" spans="1:4">
+      <c r="A8762" t="s">
+        <v>8768</v>
+      </c>
+      <c r="D8762" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8763" spans="1:4">
+      <c r="A8763" t="s">
+        <v>8769</v>
+      </c>
+      <c r="D8763" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8764" spans="1:4">
+      <c r="A8764" t="s">
+        <v>8770</v>
+      </c>
+      <c r="D8764" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8765" spans="1:4">
+      <c r="A8765" t="s">
+        <v>8771</v>
+      </c>
+      <c r="D8765" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8766" spans="1:4">
+      <c r="A8766" t="s">
+        <v>8772</v>
+      </c>
+      <c r="D8766" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8767" spans="1:4">
+      <c r="A8767" t="s">
+        <v>8773</v>
+      </c>
+      <c r="D8767" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8768" spans="1:4">
+      <c r="A8768" t="s">
+        <v>8774</v>
+      </c>
+      <c r="D8768" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8769" spans="1:4">
+      <c r="A8769" t="s">
+        <v>8775</v>
+      </c>
+      <c r="D8769" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8770" spans="1:4">
+      <c r="A8770" t="s">
+        <v>8776</v>
+      </c>
+      <c r="D8770" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8771" spans="1:4">
+      <c r="A8771" t="s">
+        <v>8777</v>
+      </c>
+      <c r="D8771" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8772" spans="1:4">
+      <c r="A8772" t="s">
+        <v>8778</v>
+      </c>
+      <c r="D8772" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8773" spans="1:4">
+      <c r="A8773" t="s">
+        <v>8779</v>
+      </c>
+      <c r="D8773" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8774" spans="1:4">
+      <c r="A8774" t="s">
+        <v>8780</v>
+      </c>
+      <c r="D8774" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8775" spans="1:4">
+      <c r="A8775" t="s">
+        <v>8781</v>
+      </c>
+      <c r="D8775" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8776" spans="1:4">
+      <c r="A8776" t="s">
+        <v>8782</v>
+      </c>
+      <c r="D8776" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8777" spans="1:4">
+      <c r="A8777" t="s">
+        <v>8783</v>
+      </c>
+      <c r="D8777" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8778" spans="1:4">
+      <c r="A8778" t="s">
+        <v>8784</v>
+      </c>
+      <c r="D8778" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17561" uniqueCount="8785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17571" uniqueCount="8790">
   <si>
     <t>code</t>
   </si>
@@ -43,6 +43,15 @@
     <t>en</t>
   </si>
   <si>
+    <t>DR-2026-000117-ETH</t>
+  </si>
+  <si>
+    <t>WF-2026-000116-KAZ</t>
+  </si>
+  <si>
+    <t>VO-2026-000115-PHL</t>
+  </si>
+  <si>
     <t>FL-2026-000114-KGZ</t>
   </si>
   <si>
@@ -103,6 +112,9 @@
     <t>TC-2026-000098-CHN</t>
   </si>
   <si>
+    <t>TC-2026-000098-LAO</t>
+  </si>
+  <si>
     <t>TC-2026-000098-VNM</t>
   </si>
   <si>
@@ -413,6 +425,9 @@
   </si>
   <si>
     <t>FL-2026-000001-MYS</t>
+  </si>
+  <si>
+    <t>DR-2025-000239-ALB</t>
   </si>
   <si>
     <t>DR-2025-000238-MDG</t>
@@ -26700,7 +26715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8778"/>
+  <dimension ref="A1:G8783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -96942,6 +96957,46 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8779" spans="1:4">
+      <c r="A8779" t="s">
+        <v>8785</v>
+      </c>
+      <c r="D8779" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8780" spans="1:4">
+      <c r="A8780" t="s">
+        <v>8786</v>
+      </c>
+      <c r="D8780" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8781" spans="1:4">
+      <c r="A8781" t="s">
+        <v>8787</v>
+      </c>
+      <c r="D8781" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8782" spans="1:4">
+      <c r="A8782" t="s">
+        <v>8788</v>
+      </c>
+      <c r="D8782" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8783" spans="1:4">
+      <c r="A8783" t="s">
+        <v>8789</v>
+      </c>
+      <c r="D8783" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17571" uniqueCount="8790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17609" uniqueCount="8809">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,63 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>WF-2026-000138-DZA</t>
+  </si>
+  <si>
+    <t>FL-2026-000137-VNM</t>
+  </si>
+  <si>
+    <t>FL-2026-000136-CHN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000135-JPN</t>
+  </si>
+  <si>
+    <t>EP-2026-000134-TCD</t>
+  </si>
+  <si>
+    <t>TC-2026-000133-CHN</t>
+  </si>
+  <si>
+    <t>TC-2026-000133-PHL</t>
+  </si>
+  <si>
+    <t>WF-2026-000132-TUN</t>
+  </si>
+  <si>
+    <t>WF-2026-000131-ESP</t>
+  </si>
+  <si>
+    <t>WF-2026-000130-ESP</t>
+  </si>
+  <si>
+    <t>WF-2026-000129-FRA</t>
+  </si>
+  <si>
+    <t>WF-2026-000128-ESP</t>
+  </si>
+  <si>
+    <t>FF-2026-000127-CHN</t>
+  </si>
+  <si>
+    <t>WF-2026-000126-TUR</t>
+  </si>
+  <si>
+    <t>FF-2026-000122-USA</t>
+  </si>
+  <si>
+    <t>FL-2026-000121-IND</t>
+  </si>
+  <si>
+    <t>FF-2026-000120-AFG</t>
+  </si>
+  <si>
+    <t>WF-2026-000119-CAN</t>
+  </si>
+  <si>
+    <t>LS-2026-000118-CHN</t>
   </si>
   <si>
     <t>DR-2026-000117-ETH</t>
@@ -26715,7 +26772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8783"/>
+  <dimension ref="A1:G8802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -96997,6 +97054,158 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8784" spans="1:4">
+      <c r="A8784" t="s">
+        <v>8790</v>
+      </c>
+      <c r="D8784" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8785" spans="1:4">
+      <c r="A8785" t="s">
+        <v>8791</v>
+      </c>
+      <c r="D8785" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8786" spans="1:4">
+      <c r="A8786" t="s">
+        <v>8792</v>
+      </c>
+      <c r="D8786" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8787" spans="1:4">
+      <c r="A8787" t="s">
+        <v>8793</v>
+      </c>
+      <c r="D8787" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8788" spans="1:4">
+      <c r="A8788" t="s">
+        <v>8794</v>
+      </c>
+      <c r="D8788" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8789" spans="1:4">
+      <c r="A8789" t="s">
+        <v>8795</v>
+      </c>
+      <c r="D8789" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8790" spans="1:4">
+      <c r="A8790" t="s">
+        <v>8796</v>
+      </c>
+      <c r="D8790" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8791" spans="1:4">
+      <c r="A8791" t="s">
+        <v>8797</v>
+      </c>
+      <c r="D8791" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8792" spans="1:4">
+      <c r="A8792" t="s">
+        <v>8798</v>
+      </c>
+      <c r="D8792" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8793" spans="1:4">
+      <c r="A8793" t="s">
+        <v>8799</v>
+      </c>
+      <c r="D8793" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8794" spans="1:4">
+      <c r="A8794" t="s">
+        <v>8800</v>
+      </c>
+      <c r="D8794" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8795" spans="1:4">
+      <c r="A8795" t="s">
+        <v>8801</v>
+      </c>
+      <c r="D8795" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8796" spans="1:4">
+      <c r="A8796" t="s">
+        <v>8802</v>
+      </c>
+      <c r="D8796" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8797" spans="1:4">
+      <c r="A8797" t="s">
+        <v>8803</v>
+      </c>
+      <c r="D8797" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8798" spans="1:4">
+      <c r="A8798" t="s">
+        <v>8804</v>
+      </c>
+      <c r="D8798" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8799" spans="1:4">
+      <c r="A8799" t="s">
+        <v>8805</v>
+      </c>
+      <c r="D8799" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8800" spans="1:4">
+      <c r="A8800" t="s">
+        <v>8806</v>
+      </c>
+      <c r="D8800" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8801" spans="1:4">
+      <c r="A8801" t="s">
+        <v>8807</v>
+      </c>
+      <c r="D8801" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8802" spans="1:4">
+      <c r="A8802" t="s">
+        <v>8808</v>
+      </c>
+      <c r="D8802" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17609" uniqueCount="8809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17621" uniqueCount="8815">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,24 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2026-000144-JPN</t>
+  </si>
+  <si>
+    <t>DR-2026-000143-COD</t>
+  </si>
+  <si>
+    <t>WF-2026-000142-GRC</t>
+  </si>
+  <si>
+    <t>FL-2026-000141-MMR</t>
+  </si>
+  <si>
+    <t>WF-2026-000140-GRC</t>
+  </si>
+  <si>
+    <t>FF-2026-000139-IND</t>
   </si>
   <si>
     <t>WF-2026-000138-DZA</t>
@@ -26772,7 +26790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8802"/>
+  <dimension ref="A1:G8808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -97206,6 +97224,54 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8803" spans="1:4">
+      <c r="A8803" t="s">
+        <v>8809</v>
+      </c>
+      <c r="D8803" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8804" spans="1:4">
+      <c r="A8804" t="s">
+        <v>8810</v>
+      </c>
+      <c r="D8804" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8805" spans="1:4">
+      <c r="A8805" t="s">
+        <v>8811</v>
+      </c>
+      <c r="D8805" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8806" spans="1:4">
+      <c r="A8806" t="s">
+        <v>8812</v>
+      </c>
+      <c r="D8806" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8807" spans="1:4">
+      <c r="A8807" t="s">
+        <v>8813</v>
+      </c>
+      <c r="D8807" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8808" spans="1:4">
+      <c r="A8808" t="s">
+        <v>8814</v>
+      </c>
+      <c r="D8808" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/GLIDENumber.xlsx
+++ b/api/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17621" uniqueCount="8815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17677" uniqueCount="8843">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,90 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2026-000170-JPN</t>
+  </si>
+  <si>
+    <t>FL-2026-000169-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2026-000168-CHN</t>
+  </si>
+  <si>
+    <t>FL-2026-000167-NPL</t>
+  </si>
+  <si>
+    <t>FL-2026-000166-CHN</t>
+  </si>
+  <si>
+    <t>FL-2026-000165-IND</t>
+  </si>
+  <si>
+    <t>FL-2026-000164-KHM</t>
+  </si>
+  <si>
+    <t>FL-2026-000163-TWN</t>
+  </si>
+  <si>
+    <t>FF-2026-000162-NPL</t>
+  </si>
+  <si>
+    <t>MS-2026-000162-CHN</t>
+  </si>
+  <si>
+    <t>TC-2026-000161-CHN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000160-AFG</t>
+  </si>
+  <si>
+    <t>DR-2026-000159-HND</t>
+  </si>
+  <si>
+    <t>FL-2026-000158-THA</t>
+  </si>
+  <si>
+    <t>TC-2026-000157-CHN</t>
+  </si>
+  <si>
+    <t>TC-2026-000157-VNM</t>
+  </si>
+  <si>
+    <t>WF-2026-000156-SRB</t>
+  </si>
+  <si>
+    <t>WF-2026-000155-BEL</t>
+  </si>
+  <si>
+    <t>WF-2026-000154-ESP</t>
+  </si>
+  <si>
+    <t>DR-2026-000153-BLZ</t>
+  </si>
+  <si>
+    <t>FF-2026-000152-SLE</t>
+  </si>
+  <si>
+    <t>EQ-2026-000150-IDN</t>
+  </si>
+  <si>
+    <t>FL-2026-000149-LKA</t>
+  </si>
+  <si>
+    <t>FL-2026-000148-CHN</t>
+  </si>
+  <si>
+    <t>WF-2026-000147-CAN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000146-COL</t>
+  </si>
+  <si>
+    <t>WF-2026-000145-TUN</t>
+  </si>
+  <si>
+    <t>TC-2026-000144-CHN</t>
   </si>
   <si>
     <t>TC-2026-000144-JPN</t>
@@ -26790,7 +26874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8808"/>
+  <dimension ref="A1:G8836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -97272,6 +97356,230 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8809" spans="1:4">
+      <c r="A8809" t="s">
+        <v>8815</v>
+      </c>
+      <c r="D8809" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8810" spans="1:4">
+      <c r="A8810" t="s">
+        <v>8816</v>
+      </c>
+      <c r="D8810" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8811" spans="1:4">
+      <c r="A8811" t="s">
+        <v>8817</v>
+      </c>
+      <c r="D8811" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8812" spans="1:4">
+      <c r="A8812" t="s">
+        <v>8818</v>
+      </c>
+      <c r="D8812" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8813" spans="1:4">
+      <c r="A8813" t="s">
+        <v>8819</v>
+      </c>
+      <c r="D8813" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8814" spans="1:4">
+      <c r="A8814" t="s">
+        <v>8820</v>
+      </c>
+      <c r="D8814" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8815" spans="1:4">
+      <c r="A8815" t="s">
+        <v>8821</v>
+      </c>
+      <c r="D8815" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8816" spans="1:4">
+      <c r="A8816" t="s">
+        <v>8822</v>
+      </c>
+      <c r="D8816" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8817" spans="1:4">
+      <c r="A8817" t="s">
+        <v>8823</v>
+      </c>
+      <c r="D8817" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8818" spans="1:4">
+      <c r="A8818" t="s">
+        <v>8824</v>
+      </c>
+      <c r="D8818" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8819" spans="1:4">
+      <c r="A8819" t="s">
+        <v>8825</v>
+      </c>
+      <c r="D8819" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8820" spans="1:4">
+      <c r="A8820" t="s">
+        <v>8826</v>
+      </c>
+      <c r="D8820" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8821" spans="1:4">
+      <c r="A8821" t="s">
+        <v>8827</v>
+      </c>
+      <c r="D8821" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8822" spans="1:4">
+      <c r="A8822" t="s">
+        <v>8828</v>
+      </c>
+      <c r="D8822" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8823" spans="1:4">
+      <c r="A8823" t="s">
+        <v>8829</v>
+      </c>
+      <c r="D8823" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8824" spans="1:4">
+      <c r="A8824" t="s">
+        <v>8830</v>
+      </c>
+      <c r="D8824" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8825" spans="1:4">
+      <c r="A8825" t="s">
+        <v>8831</v>
+      </c>
+      <c r="D8825" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8826" spans="1:4">
+      <c r="A8826" t="s">
+        <v>8832</v>
+      </c>
+      <c r="D8826" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8827" spans="1:4">
+      <c r="A8827" t="s">
+        <v>8833</v>
+      </c>
+      <c r="D8827" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8828" spans="1:4">
+      <c r="A8828" t="s">
+        <v>8834</v>
+      </c>
+      <c r="D8828" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8829" spans="1:4">
+      <c r="A8829" t="s">
+        <v>8835</v>
+      </c>
+      <c r="D8829" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8830" spans="1:4">
+      <c r="A8830" t="s">
+        <v>8836</v>
+      </c>
+      <c r="D8830" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8831" spans="1:4">
+      <c r="A8831" t="s">
+        <v>8837</v>
+      </c>
+      <c r="D8831" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8832" spans="1:4">
+      <c r="A8832" t="s">
+        <v>8838</v>
+      </c>
+      <c r="D8832" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8833" spans="1:4">
+      <c r="A8833" t="s">
+        <v>8839</v>
+      </c>
+      <c r="D8833" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8834" spans="1:4">
+      <c r="A8834" t="s">
+        <v>8840</v>
+      </c>
+      <c r="D8834" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8835" spans="1:4">
+      <c r="A8835" t="s">
+        <v>8841</v>
+      </c>
+      <c r="D8835" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8836" spans="1:4">
+      <c r="A8836" t="s">
+        <v>8842</v>
+      </c>
+      <c r="D8836" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
